--- a/assets/xlsx/self_links.xlsx
+++ b/assets/xlsx/self_links.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28500" windowHeight="9435" tabRatio="400"/>
+    <workbookView windowWidth="28800" windowHeight="12300" tabRatio="400"/>
   </bookViews>
   <sheets>
     <sheet name="links" sheetId="1" r:id="rId1"/>
@@ -101,7 +101,7 @@
     <t>http://www.cppcc.gov.cn/images/favicon.ico</t>
   </si>
   <si>
-    <t>中国政协网,http://www.cppcc.gov.cn/</t>
+    <t>中国政协网,https://www.cppcc.gov.cn/</t>
   </si>
   <si>
     <t>北京市政协</t>
@@ -110,25 +110,25 @@
     <t>直辖市</t>
   </si>
   <si>
-    <t xml:space="preserve">官网,http://www.bjzx.gov.cn/ </t>
+    <t xml:space="preserve">官网,https://www.bjzx.gov.cn/ </t>
   </si>
   <si>
     <t>天津市政协</t>
   </si>
   <si>
-    <t>官网,http://www.tjszx.gov.cn/</t>
+    <t>官网,https://www.tjszx.gov.cn/</t>
   </si>
   <si>
     <t>上海市政协</t>
   </si>
   <si>
-    <t>官网,http://www.shszx.gov.cn/</t>
+    <t>官网,https://www.shszx.gov.cn/</t>
   </si>
   <si>
     <t>重庆市政协</t>
   </si>
   <si>
-    <t>官网,http://www.cqzx.gov.cn/</t>
+    <t>官网,https://www.cqzx.gov.cn/</t>
   </si>
   <si>
     <t>广西壮族自治区政协</t>
@@ -137,7 +137,7 @@
     <t>自治区</t>
   </si>
   <si>
-    <t xml:space="preserve">官网,http://www.gxzx.gov.cn/ </t>
+    <t xml:space="preserve">官网,https://www.gxzx.gov.cn/ </t>
   </si>
   <si>
     <t>内蒙古自治区政协</t>
@@ -146,25 +146,25 @@
     <t>http://www.nmgzx.gov.cn/favicon.ico</t>
   </si>
   <si>
-    <t>官网,http://www.nmgzx.gov.cn/webpage/homepage/index.html</t>
+    <t>官网,https://www.nmgzx.gov.cn/webpage/homepage/index.html</t>
   </si>
   <si>
     <t>宁夏回族自治区政协</t>
   </si>
   <si>
-    <t xml:space="preserve">官网,http://www.nxzx.gov.cn/  </t>
+    <t xml:space="preserve">官网,https://www.nxzx.gov.cn/  </t>
   </si>
   <si>
     <t>西藏自治区政协</t>
   </si>
   <si>
-    <t>官网,http://www.xizangzx.gov.cn</t>
+    <t>官网,https://www.xizangzx.gov.cn</t>
   </si>
   <si>
     <t>新疆维吾尔自治区政协</t>
   </si>
   <si>
-    <t xml:space="preserve">官网,http://www.xjzx.gov.cn/  </t>
+    <t xml:space="preserve">官网,https://www.xjzx.gov.cn/  </t>
   </si>
   <si>
     <t>安徽省政协</t>
@@ -173,19 +173,19 @@
     <t>省级</t>
   </si>
   <si>
-    <t>官网,http://www.ahzx.gov.cn/</t>
+    <t>官网,https://www.ahzx.gov.cn/</t>
   </si>
   <si>
     <t>福建省政协</t>
   </si>
   <si>
-    <t>官网,http://www.fjzx.gov.cn/</t>
+    <t>官网,https://www.fjzx.gov.cn/</t>
   </si>
   <si>
     <t>甘肃省政协</t>
   </si>
   <si>
-    <t>官网,http://www.gszx.gov.cn/</t>
+    <t>官网,https://www.gszx.gov.cn/</t>
   </si>
   <si>
     <t>广东省政协</t>
@@ -194,7 +194,7 @@
     <t>省级,广东</t>
   </si>
   <si>
-    <t>官网,http://www.gdzxb.gov.cn/</t>
+    <t>官网,https://www.gdzxb.gov.cn/</t>
   </si>
   <si>
     <t>广州市政协</t>
@@ -212,13 +212,13 @@
     <t>深圳市政协</t>
   </si>
   <si>
-    <t>官网,http://www.szzx.gov.cn/</t>
+    <t>官网,https://www.szzx.gov.cn/</t>
   </si>
   <si>
     <t>珠海市政协</t>
   </si>
   <si>
-    <t>官网,http://www.zhzx.gov.cn/</t>
+    <t>官网,https://www.zhzx.gov.cn/</t>
   </si>
   <si>
     <t>汕头市政协</t>
@@ -227,7 +227,7 @@
     <t>市级,汕头,广东</t>
   </si>
   <si>
-    <t>官网,http://stzx.shantou.gov.cn/</t>
+    <t>官网,https://stzx.shantou.gov.cn/</t>
   </si>
   <si>
     <t>金平区政协</t>
@@ -239,61 +239,61 @@
     <t>区级,汕头,广东</t>
   </si>
   <si>
-    <t>官网,http://www.jpzx.gov.cn/welcome</t>
+    <t>官网,https://www.jpzx.gov.cn/welcome</t>
   </si>
   <si>
     <t>佛山市政协</t>
   </si>
   <si>
-    <t>官网,http://www.fszx.gov.cn/</t>
+    <t>官网,https://www.fszx.gov.cn/</t>
   </si>
   <si>
     <t>韶关市政协</t>
   </si>
   <si>
-    <t>官网,http://www.sgzxb.gov.cn/</t>
+    <t>官网,https://www.sgzxb.gov.cn/</t>
   </si>
   <si>
     <t>河源市政协</t>
   </si>
   <si>
-    <t>官网,http://www.gdhyzx.gov.cn/hyzx/index.html</t>
+    <t>官网,https://www.gdhyzx.gov.cn/hyzx/index.html</t>
   </si>
   <si>
     <t>梅州市政协</t>
   </si>
   <si>
-    <t>官网,http://www.mzzx.gov.cn/</t>
+    <t>官网,https://www.mzzx.gov.cn/</t>
   </si>
   <si>
     <t>惠州市政协</t>
   </si>
   <si>
-    <t>官网,http://zx.huizhou.gov.cn/</t>
+    <t>官网,https://zx.huizhou.gov.cn/</t>
   </si>
   <si>
     <t>汕尾市政协</t>
   </si>
   <si>
-    <t>官网,http://www.swzx.gov.cn/</t>
+    <t>官网,https://www.swzx.gov.cn/</t>
   </si>
   <si>
     <t>东莞市政协</t>
   </si>
   <si>
-    <t>官网,http://dgzx.dg.gov.cn/</t>
+    <t>官网,https://dgzx.dg.gov.cn/</t>
   </si>
   <si>
     <t>中山市政协</t>
   </si>
   <si>
-    <t>官网,http://zszx.zsnews.cn/</t>
+    <t>官网,https://zszx.zsnews.cn/</t>
   </si>
   <si>
     <t>江门市政协</t>
   </si>
   <si>
-    <t>官网,http://zx.jiangmen.cn/</t>
+    <t>官网,https://zx.jiangmen.cn/</t>
   </si>
   <si>
     <t>阳江市政协</t>
@@ -308,37 +308,37 @@
     <t>https://www.google.com/s2/favicons?domain=http://www.gdzjzx.gov.cn/</t>
   </si>
   <si>
-    <t>官网,http://www.gdzjzx.gov.cn/</t>
+    <t>官网,https://www.gdzjzx.gov.cn/</t>
   </si>
   <si>
     <t>茂名市政协</t>
   </si>
   <si>
-    <t>官网,http://zx.maoming.gov.cn/website/main/jsp/index.jsp</t>
+    <t>官网,https://zx.maoming.gov.cn/website/main/jsp/index.jsp</t>
   </si>
   <si>
     <t>肇庆市政协</t>
   </si>
   <si>
-    <t>官网,http://zqzx.gov.cn/index.html</t>
+    <t>官网,https://zqzx.gov.cn/index.html</t>
   </si>
   <si>
     <t>潮州市政协</t>
   </si>
   <si>
-    <t>官网,http://czzx.gov.cn/</t>
+    <t>官网,https://czzx.gov.cn/</t>
   </si>
   <si>
     <t>揭阳市政协</t>
   </si>
   <si>
-    <t xml:space="preserve">官网,http://www.jieyangzhengxie.gov.cn/ </t>
+    <t xml:space="preserve">官网,https://www.jieyangzhengxie.gov.cn/ </t>
   </si>
   <si>
     <t>云浮市政协</t>
   </si>
   <si>
-    <t>官网,http://zx.yunfu.gov.cn/</t>
+    <t>官网,https://zx.yunfu.gov.cn/</t>
   </si>
   <si>
     <t>贵州省政协</t>
@@ -350,13 +350,13 @@
     <t>海南省政协</t>
   </si>
   <si>
-    <t xml:space="preserve">官网,http://www.hainanzx.gov.cn/default.html </t>
+    <t xml:space="preserve">官网,https://www.hainanzx.gov.cn/default.html </t>
   </si>
   <si>
     <t>河北省政协</t>
   </si>
   <si>
-    <t xml:space="preserve">官网,http://www.hebzx.gov.cn/ </t>
+    <t xml:space="preserve">官网,https://www.hebzx.gov.cn/ </t>
   </si>
   <si>
     <t>河南省政协</t>
@@ -365,13 +365,13 @@
     <t>https://www.google.com/s2/favicons?domain=http://www.hnzx.gov.cn/</t>
   </si>
   <si>
-    <t>官网,http://www.hnzx.gov.cn/</t>
+    <t>官网,https://www.hnzx.gov.cn/</t>
   </si>
   <si>
     <t>黑龙江省政协</t>
   </si>
   <si>
-    <t>官网,http://www.hljzx.gov.cn/</t>
+    <t>官网,https://www.hljzx.gov.cn/</t>
   </si>
   <si>
     <t>哈尔滨市政协</t>
@@ -395,7 +395,7 @@
     <t>武汉市政协</t>
   </si>
   <si>
-    <t xml:space="preserve">官网,http://www.whzx.org.cn/  </t>
+    <t xml:space="preserve">官网,https://www.whzx.org.cn/  </t>
   </si>
   <si>
     <t>湖南省政协</t>
@@ -407,13 +407,13 @@
     <t>吉林省政协</t>
   </si>
   <si>
-    <t>官网,http://www.jlzx.gov.cn/</t>
+    <t>官网,https://www.jlzx.gov.cn/</t>
   </si>
   <si>
     <t>江苏省政协</t>
   </si>
   <si>
-    <t>官网,http://www.jszx.gov.cn/</t>
+    <t>官网,https://www.jszx.gov.cn/</t>
   </si>
   <si>
     <t>江西省政协</t>
@@ -425,49 +425,49 @@
     <t>辽宁省政协</t>
   </si>
   <si>
-    <t>官网,http://www.lnzx.gov.cn/</t>
+    <t>官网,https://www.lnzx.gov.cn/</t>
   </si>
   <si>
     <t>青海省政协</t>
   </si>
   <si>
-    <t>官网,http://www.qhszx.gov.cn/</t>
+    <t>官网,https://www.qhszx.gov.cn/</t>
   </si>
   <si>
     <t>山东省政协</t>
   </si>
   <si>
-    <t>官网,http://www.sdzx.gov.cn/</t>
+    <t>官网,https://www.sdzx.gov.cn/</t>
   </si>
   <si>
     <t>山西省政协</t>
   </si>
   <si>
-    <t>官网,http://www.shanxizx.gov.cn/</t>
+    <t>官网,https://www.shanxizx.gov.cn/</t>
   </si>
   <si>
     <t>陕西省政协</t>
   </si>
   <si>
-    <t>官网,http://www.sxzx.gov.cn/</t>
+    <t>官网,https://www.sxzx.gov.cn/</t>
   </si>
   <si>
     <t>四川省政协</t>
   </si>
   <si>
-    <t>官网,http://www.sczx.gov.cn/</t>
+    <t>官网,https://www.sczx.gov.cn/</t>
   </si>
   <si>
     <t>云南省政协</t>
   </si>
   <si>
-    <t>官网,http://www.ynzx.gov.cn/</t>
+    <t>官网,https://www.ynzx.gov.cn/</t>
   </si>
   <si>
     <t>浙江省政协</t>
   </si>
   <si>
-    <t>官网,http://www.zjzx.gov.cn/</t>
+    <t>官网,https://www.zjzx.gov.cn/</t>
   </si>
   <si>
     <t>资讯媒体</t>
@@ -479,7 +479,7 @@
     <t>中央媒体</t>
   </si>
   <si>
-    <t>官网,http://www.cri.cn</t>
+    <t>官网,https://www.cri.cn</t>
   </si>
   <si>
     <t>中国日报网</t>
@@ -488,19 +488,19 @@
     <t>http://www.chinadaily.com.cn/favicon.ico</t>
   </si>
   <si>
-    <t>官网,http://www.chinadaily.com.cn</t>
+    <t>官网,https://www.chinadaily.com.cn</t>
   </si>
   <si>
     <t>人民网</t>
   </si>
   <si>
-    <t>官网,http://www.people.com.cn/</t>
+    <t>官网,https://www.people.com.cn/</t>
   </si>
   <si>
     <t>新华网</t>
   </si>
   <si>
-    <t>官网,http://www.xinhuanet.com</t>
+    <t>官网,https://www.xinhuanet.com</t>
   </si>
   <si>
     <t>中国军网</t>
@@ -509,13 +509,13 @@
     <t>解放军报社</t>
   </si>
   <si>
-    <t>官网,http://www.81.cn/</t>
+    <t>官网,https://www.81.cn/</t>
   </si>
   <si>
     <t>求是网</t>
   </si>
   <si>
-    <t>官网,http://www.qstheory.cn</t>
+    <t>官网,https://www.qstheory.cn</t>
   </si>
   <si>
     <t>光明网</t>
@@ -524,13 +524,13 @@
     <t>http://www.gmw.cn/favicon.ico</t>
   </si>
   <si>
-    <t>官网,http://www.gmw.cn/</t>
+    <t>官网,https://www.gmw.cn/</t>
   </si>
   <si>
     <t>中国经济网</t>
   </si>
   <si>
-    <t>官网,http://www.ce.cn</t>
+    <t>官网,https://www.ce.cn</t>
   </si>
   <si>
     <t>中国新闻网</t>
@@ -539,7 +539,7 @@
     <t>中新社</t>
   </si>
   <si>
-    <t>官网,http://www.chinanews.com</t>
+    <t>官网,https://www.chinanews.com</t>
   </si>
   <si>
     <t>法制网</t>
@@ -548,7 +548,7 @@
     <t>法制日报</t>
   </si>
   <si>
-    <t>官网,http://www.legaldaily.com.cn/</t>
+    <t>官网,https://www.legaldaily.com.cn/</t>
   </si>
   <si>
     <t>中国农网</t>
@@ -557,7 +557,7 @@
     <t>农民日报</t>
   </si>
   <si>
-    <t>官网,http://www.farmer.com.cn/</t>
+    <t>官网,https://www.farmer.com.cn/</t>
   </si>
   <si>
     <t>中国妇女网</t>
@@ -566,7 +566,7 @@
     <t>中国妇女报</t>
   </si>
   <si>
-    <t>官网,http://www.cnwomen.com.cn/</t>
+    <t>官网,https://www.cnwomen.com.cn/</t>
   </si>
   <si>
     <t>中青在线</t>
@@ -575,7 +575,7 @@
     <t>中国青年报</t>
   </si>
   <si>
-    <t>官网,http://www.cyol.com</t>
+    <t>官网,https://www.cyol.com</t>
   </si>
   <si>
     <t>中工网</t>
@@ -584,13 +584,13 @@
     <t>工人日报</t>
   </si>
   <si>
-    <t>官网,http://www.workercn.cn</t>
+    <t>官网,https://www.workercn.cn</t>
   </si>
   <si>
     <t>中国纪检监察报</t>
   </si>
   <si>
-    <t>官网,http://www.jjjcb.cn</t>
+    <t>官网,https://www.jjjcb.cn</t>
   </si>
   <si>
     <t>中国科技网</t>
@@ -599,7 +599,7 @@
     <t>科技日报</t>
   </si>
   <si>
-    <t>官网,http://www.stdaily.com</t>
+    <t>官网,https://www.stdaily.com</t>
   </si>
   <si>
     <t>央视网</t>
@@ -617,7 +617,7 @@
     <t>http://www.cnr.cn/favicon.ico,#FFFFFF</t>
   </si>
   <si>
-    <t>官网,http://www.cnr.cn/;公众号,http://weixin.qq.com/r/Qhy_pnDE5y2YrTTF90lQ;微博,https://weibo.com/u/1683472727;听中国微博,https://weibo.com/u/1867571077</t>
+    <t>官网,https://www.cnr.cn/;公众号,https://weixin.qq.com/r/Qhy_pnDE5y2YrTTF90lQ;微博,https://weibo.com/u/1683472727;听中国微博,https://weibo.com/u/1867571077</t>
   </si>
   <si>
     <t>常用入口</t>
@@ -2336,7 +2336,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:H129"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
@@ -2376,7 +2376,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" hidden="1" spans="1:8">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2399,7 +2399,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" hidden="1" spans="1:8">
       <c r="A3">
         <v>0</v>
       </c>
@@ -2422,7 +2422,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" hidden="1" spans="1:8">
       <c r="A4">
         <v>0</v>
       </c>
@@ -2445,7 +2445,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" hidden="1" spans="1:8">
       <c r="A5">
         <v>0</v>
       </c>
@@ -2755,7 +2755,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" hidden="1" spans="1:8">
       <c r="A20">
         <v>17</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" hidden="1" spans="1:8">
       <c r="A34">
         <v>31</v>
       </c>
@@ -3184,7 +3184,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" hidden="1" spans="1:8">
       <c r="A41">
         <v>38</v>
       </c>
@@ -3287,7 +3287,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" hidden="1" spans="1:8">
       <c r="A46">
         <v>43</v>
       </c>
@@ -3307,7 +3307,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" hidden="1" spans="1:8">
       <c r="A47">
         <v>44</v>
       </c>
@@ -3350,7 +3350,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" hidden="1" spans="1:8">
       <c r="A49">
         <v>46</v>
       </c>
@@ -3410,7 +3410,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" hidden="1" spans="1:8">
       <c r="A52">
         <v>49</v>
       </c>
@@ -3941,7 +3941,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" hidden="1" spans="1:8">
       <c r="A77">
         <v>74</v>
       </c>
@@ -3987,7 +3987,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" hidden="1" spans="1:8">
       <c r="A79">
         <v>76</v>
       </c>
@@ -4013,7 +4013,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" hidden="1" spans="1:8">
       <c r="A80">
         <v>77</v>
       </c>
@@ -4039,7 +4039,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" hidden="1" spans="1:8">
       <c r="A81">
         <v>78</v>
       </c>
@@ -4065,7 +4065,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" hidden="1" spans="1:8">
       <c r="A82">
         <v>79</v>
       </c>
@@ -4091,7 +4091,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" hidden="1" spans="1:8">
       <c r="A83">
         <v>80</v>
       </c>
@@ -4117,7 +4117,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" hidden="1" spans="1:8">
       <c r="A84">
         <v>81</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" hidden="1" spans="1:8">
       <c r="A85">
         <v>82</v>
       </c>
@@ -4169,7 +4169,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" hidden="1" spans="1:8">
       <c r="A86">
         <v>83</v>
       </c>
@@ -4195,7 +4195,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" hidden="1" spans="1:8">
       <c r="A87">
         <v>84</v>
       </c>
@@ -4218,7 +4218,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" hidden="1" spans="1:8">
       <c r="A88">
         <v>85</v>
       </c>
@@ -4241,7 +4241,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" hidden="1" spans="1:8">
       <c r="A89">
         <v>86</v>
       </c>
@@ -4267,7 +4267,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" hidden="1" spans="1:8">
       <c r="A90">
         <v>87</v>
       </c>
@@ -4293,7 +4293,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" hidden="1" spans="1:8">
       <c r="A91">
         <v>88</v>
       </c>
@@ -4319,7 +4319,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" hidden="1" spans="1:8">
       <c r="A92">
         <v>89</v>
       </c>
@@ -4345,7 +4345,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" hidden="1" spans="1:8">
       <c r="A93">
         <v>90</v>
       </c>
@@ -4371,7 +4371,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" hidden="1" spans="1:8">
       <c r="A94">
         <v>91</v>
       </c>
@@ -4397,7 +4397,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" hidden="1" spans="1:8">
       <c r="A95">
         <v>92</v>
       </c>
@@ -4423,7 +4423,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" hidden="1" spans="1:8">
       <c r="A96">
         <v>93</v>
       </c>
@@ -4449,7 +4449,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" hidden="1" spans="1:8">
       <c r="A97">
         <v>94</v>
       </c>
@@ -4475,7 +4475,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" hidden="1" spans="1:8">
       <c r="A98">
         <v>95</v>
       </c>
@@ -4501,7 +4501,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" hidden="1" spans="1:8">
       <c r="A99">
         <v>96</v>
       </c>
@@ -4527,7 +4527,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" hidden="1" spans="1:8">
       <c r="A100">
         <v>97</v>
       </c>
@@ -4553,7 +4553,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" hidden="1" spans="1:8">
       <c r="A101">
         <v>98</v>
       </c>
@@ -4579,7 +4579,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" hidden="1" spans="1:8">
       <c r="A102">
         <v>99</v>
       </c>
@@ -4605,7 +4605,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" hidden="1" spans="1:8">
       <c r="A103">
         <v>100</v>
       </c>
@@ -4631,7 +4631,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" hidden="1" spans="1:8">
       <c r="A104">
         <v>101</v>
       </c>
@@ -4657,7 +4657,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" hidden="1" spans="1:8">
       <c r="A105">
         <v>102</v>
       </c>
@@ -4683,7 +4683,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" hidden="1" spans="1:8">
       <c r="A106">
         <v>103</v>
       </c>
@@ -4709,7 +4709,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" hidden="1" spans="1:8">
       <c r="A107">
         <v>104</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" hidden="1" spans="1:8">
       <c r="A108">
         <v>105</v>
       </c>
@@ -4761,7 +4761,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" hidden="1" spans="1:8">
       <c r="A109">
         <v>106</v>
       </c>
@@ -4787,7 +4787,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" hidden="1" spans="1:8">
       <c r="A110">
         <v>107</v>
       </c>
@@ -4813,7 +4813,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" hidden="1" spans="1:8">
       <c r="A111">
         <v>108</v>
       </c>
@@ -4839,7 +4839,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" hidden="1" spans="1:8">
       <c r="A112">
         <v>109</v>
       </c>
@@ -4865,7 +4865,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" hidden="1" spans="1:8">
       <c r="A113">
         <v>110</v>
       </c>
@@ -4891,7 +4891,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" hidden="1" spans="1:8">
       <c r="A114">
         <v>111</v>
       </c>
@@ -4917,7 +4917,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" hidden="1" spans="1:8">
       <c r="A115">
         <v>112</v>
       </c>
@@ -4943,7 +4943,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" hidden="1" spans="1:8">
       <c r="A116">
         <v>113</v>
       </c>
@@ -4969,7 +4969,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" hidden="1" spans="1:8">
       <c r="A117">
         <v>114</v>
       </c>
@@ -4995,7 +4995,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" hidden="1" spans="1:8">
       <c r="A118">
         <v>115</v>
       </c>
@@ -5021,7 +5021,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" hidden="1" spans="1:8">
       <c r="A119">
         <v>116</v>
       </c>
@@ -5047,7 +5047,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" hidden="1" spans="1:8">
       <c r="A120">
         <v>117</v>
       </c>
@@ -5070,7 +5070,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" hidden="1" spans="1:8">
       <c r="A121">
         <v>118</v>
       </c>
@@ -5093,7 +5093,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" hidden="1" spans="1:8">
       <c r="A122">
         <v>119</v>
       </c>
@@ -5116,7 +5116,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" hidden="1" spans="1:8">
       <c r="A123">
         <v>120</v>
       </c>
@@ -5139,7 +5139,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" hidden="1" spans="1:8">
       <c r="A124">
         <v>121</v>
       </c>
@@ -5165,7 +5165,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" hidden="1" spans="1:8">
       <c r="A125">
         <v>122</v>
       </c>
@@ -5191,7 +5191,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" hidden="1" spans="1:8">
       <c r="A126">
         <v>123</v>
       </c>
@@ -5217,7 +5217,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" hidden="1" spans="1:8">
       <c r="A127">
         <v>124</v>
       </c>
@@ -5243,7 +5243,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" hidden="1" spans="1:8">
       <c r="A128">
         <v>125</v>
       </c>
@@ -5266,7 +5266,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" hidden="1" spans="1:8">
       <c r="A129">
         <v>126</v>
       </c>
@@ -5294,6 +5294,75 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H129" etc:filterBottomFollowUsedRange="0">
+    <filterColumn colId="7">
+      <filters>
+        <filter val="官网,http://czzx.gov.cn/"/>
+        <filter val="官网,http://www.chinadaily.com.cn"/>
+        <filter val="官网,http://www.xinhuanet.com"/>
+        <filter val="官网,http://zx.maoming.gov.cn/website/main/jsp/index.jsp"/>
+        <filter val="官网,http://www.jpzx.gov.cn/welcome"/>
+        <filter val="官网,http://www.cnr.cn/;公众号,http://weixin.qq.com/r/Qhy_pnDE5y2YrTTF90lQ;微博,https://weibo.com/u/1683472727;听中国微博,https://weibo.com/u/1867571077"/>
+        <filter val="官网,http://www.people.com.cn/"/>
+        <filter val="官网,http://www.nmgzx.gov.cn/webpage/homepage/index.html"/>
+        <filter val="官网,http://www.workercn.cn"/>
+        <filter val="中国政协网,http://www.cppcc.gov.cn/"/>
+        <filter val="官网,http://www.hainanzx.gov.cn/default.html"/>
+        <filter val="官网,http://www.qstheory.cn"/>
+        <filter val="官网,http://www.shanxizx.gov.cn/"/>
+        <filter val="官网,http://www.tjszx.gov.cn/"/>
+        <filter val="官网,http://www.jieyangzhengxie.gov.cn/"/>
+        <filter val="官网,http://www.81.cn/"/>
+        <filter val="官网,http://www.qhszx.gov.cn/"/>
+        <filter val="官网,http://zx.jiangmen.cn/"/>
+        <filter val="官网,http://www.shszx.gov.cn/"/>
+        <filter val="官网,http://www.sgzxb.gov.cn/"/>
+        <filter val="官网,http://www.cyol.com"/>
+        <filter val="官网,http://www.gdzxb.gov.cn/"/>
+        <filter val="官网,http://www.hljzx.gov.cn/"/>
+        <filter val="官网,http://www.hebzx.gov.cn/"/>
+        <filter val="官网,http://zx.huizhou.gov.cn/"/>
+        <filter val="官网,http://zqzx.gov.cn/index.html"/>
+        <filter val="官网,http://www.chinanews.com"/>
+        <filter val="官网,http://www.ce.cn"/>
+        <filter val="官网,http://www.bjzx.gov.cn/"/>
+        <filter val="官网,http://www.ahzx.gov.cn/"/>
+        <filter val="官网,http://www.ynzx.gov.cn/"/>
+        <filter val="官网,http://www.jlzx.gov.cn/"/>
+        <filter val="官网,http://www.jszx.gov.cn/"/>
+        <filter val="官网,http://www.gxzx.gov.cn/"/>
+        <filter val="官网,http://www.gszx.gov.cn/"/>
+        <filter val="官网,http://www.hnzx.gov.cn/"/>
+        <filter val="官网,http://www.fjzx.gov.cn/"/>
+        <filter val="官网,http://www.fszx.gov.cn/"/>
+        <filter val="官网,http://www.cqzx.gov.cn/"/>
+        <filter val="官网,http://www.sdzx.gov.cn/"/>
+        <filter val="官网,http://www.sczx.gov.cn/"/>
+        <filter val="官网,http://www.zjzx.gov.cn/"/>
+        <filter val="官网,http://www.zhzx.gov.cn/"/>
+        <filter val="官网,http://www.xjzx.gov.cn/"/>
+        <filter val="官网,http://www.szzx.gov.cn/"/>
+        <filter val="官网,http://www.sxzx.gov.cn/"/>
+        <filter val="官网,http://www.swzx.gov.cn/"/>
+        <filter val="官网,http://www.legaldaily.com.cn/"/>
+        <filter val="官网,http://www.mzzx.gov.cn/"/>
+        <filter val="官网,http://www.nxzx.gov.cn/"/>
+        <filter val="官网,http://www.lnzx.gov.cn/"/>
+        <filter val="官网,http://www.farmer.com.cn/"/>
+        <filter val="官网,http://www.gdhyzx.gov.cn/hyzx/index.html"/>
+        <filter val="官网,http://www.stdaily.com"/>
+        <filter val="官网,http://www.jjjcb.cn"/>
+        <filter val="官网,http://www.xizangzx.gov.cn"/>
+        <filter val="官网,http://www.gmw.cn/"/>
+        <filter val="官网,http://zszx.zsnews.cn/"/>
+        <filter val="官网,http://www.gdzjzx.gov.cn/"/>
+        <filter val="官网,http://www.whzx.org.cn/"/>
+        <filter val="官网,http://stzx.shantou.gov.cn/"/>
+        <filter val="官网,http://www.cnwomen.com.cn/"/>
+        <filter val="官网,http://www.cri.cn"/>
+        <filter val="官网,http://dgzx.dg.gov.cn/"/>
+        <filter val="官网,http://zx.yunfu.gov.cn/"/>
+      </filters>
+    </filterColumn>
     <sortState ref="A1:H129">
       <sortCondition ref="A1"/>
     </sortState>
@@ -5305,7 +5374,7 @@
     <hyperlink ref="F4" r:id="rId3" display="https://zhengxie.com.cn/assets/images/12377-3-07.webp" tooltip="https://zhengxie.com.cn/assets/images/12377-3-07.webp"/>
     <hyperlink ref="F5" r:id="rId4" display="https://zhengxie.com.cn/assets/images/12377-3-04.webp" tooltip="https://zhengxie.com.cn/assets/images/12377-3-04.webp"/>
     <hyperlink ref="F6" r:id="rId5" display="http://www.cppcc.gov.cn/images/favicon.ico"/>
-    <hyperlink ref="H6" r:id="rId6" display="中国政协网,http://www.cppcc.gov.cn/"/>
+    <hyperlink ref="H6" r:id="rId6" display="中国政协网,https://www.cppcc.gov.cn/"/>
     <hyperlink ref="F12" r:id="rId7" display="http://www.nmgzx.gov.cn/favicon.ico"/>
     <hyperlink ref="F20" r:id="rId8" display="https://www.gzzx.gov.cn/images/iconcf134.ico"/>
     <hyperlink ref="F24" r:id="rId9" display="http://www.jpzx.gov.cn/favicon.ico"/>

--- a/assets/xlsx/self_links.xlsx
+++ b/assets/xlsx/self_links.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12300" tabRatio="400"/>
+    <workbookView windowWidth="28800" windowHeight="11700" tabRatio="400"/>
   </bookViews>
   <sheets>
     <sheet name="links" sheetId="1" r:id="rId1"/>
@@ -92,10 +92,10 @@
     <t>政协</t>
   </si>
   <si>
-    <t>中国人民政治协商会议全国委员会</t>
-  </si>
-  <si>
-    <t>The National Committee of the Chinese People's Political Consultative Conference</t>
+    <t>全国政协</t>
+  </si>
+  <si>
+    <t>中国人民政治协商会议全国委员会 The National Committee of the Chinese People's Political Consultative Conference</t>
   </si>
   <si>
     <t>http://www.cppcc.gov.cn/images/favicon.ico</t>
@@ -2336,7 +2336,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr filterMode="1"/>
+  <sheetPr/>
   <dimension ref="A1:H129"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelCol="7"/>
   <cols>
@@ -2376,7 +2376,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" hidden="1" spans="1:8">
+    <row r="2" spans="1:8">
       <c r="A2">
         <v>0</v>
       </c>
@@ -2399,7 +2399,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" hidden="1" spans="1:8">
+    <row r="3" spans="1:8">
       <c r="A3">
         <v>0</v>
       </c>
@@ -2422,7 +2422,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" hidden="1" spans="1:8">
+    <row r="4" spans="1:8">
       <c r="A4">
         <v>0</v>
       </c>
@@ -2445,7 +2445,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" hidden="1" spans="1:8">
+    <row r="5" spans="1:8">
       <c r="A5">
         <v>0</v>
       </c>
@@ -2755,7 +2755,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" hidden="1" spans="1:8">
+    <row r="20" spans="1:8">
       <c r="A20">
         <v>17</v>
       </c>
@@ -3041,7 +3041,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="34" hidden="1" spans="1:8">
+    <row r="34" spans="1:8">
       <c r="A34">
         <v>31</v>
       </c>
@@ -3184,7 +3184,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="41" hidden="1" spans="1:8">
+    <row r="41" spans="1:8">
       <c r="A41">
         <v>38</v>
       </c>
@@ -3287,7 +3287,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="46" hidden="1" spans="1:8">
+    <row r="46" spans="1:8">
       <c r="A46">
         <v>43</v>
       </c>
@@ -3307,7 +3307,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="47" hidden="1" spans="1:8">
+    <row r="47" spans="1:8">
       <c r="A47">
         <v>44</v>
       </c>
@@ -3350,7 +3350,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="49" hidden="1" spans="1:8">
+    <row r="49" spans="1:8">
       <c r="A49">
         <v>46</v>
       </c>
@@ -3410,7 +3410,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="52" hidden="1" spans="1:8">
+    <row r="52" spans="1:8">
       <c r="A52">
         <v>49</v>
       </c>
@@ -3941,7 +3941,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="77" hidden="1" spans="1:8">
+    <row r="77" spans="1:8">
       <c r="A77">
         <v>74</v>
       </c>
@@ -3987,7 +3987,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="79" hidden="1" spans="1:8">
+    <row r="79" spans="1:8">
       <c r="A79">
         <v>76</v>
       </c>
@@ -4013,7 +4013,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="80" hidden="1" spans="1:8">
+    <row r="80" spans="1:8">
       <c r="A80">
         <v>77</v>
       </c>
@@ -4039,7 +4039,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="81" hidden="1" spans="1:8">
+    <row r="81" spans="1:8">
       <c r="A81">
         <v>78</v>
       </c>
@@ -4065,7 +4065,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="82" hidden="1" spans="1:8">
+    <row r="82" spans="1:8">
       <c r="A82">
         <v>79</v>
       </c>
@@ -4091,7 +4091,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="83" hidden="1" spans="1:8">
+    <row r="83" spans="1:8">
       <c r="A83">
         <v>80</v>
       </c>
@@ -4117,7 +4117,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="84" hidden="1" spans="1:8">
+    <row r="84" spans="1:8">
       <c r="A84">
         <v>81</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="85" hidden="1" spans="1:8">
+    <row r="85" spans="1:8">
       <c r="A85">
         <v>82</v>
       </c>
@@ -4169,7 +4169,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="86" hidden="1" spans="1:8">
+    <row r="86" spans="1:8">
       <c r="A86">
         <v>83</v>
       </c>
@@ -4195,7 +4195,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="87" hidden="1" spans="1:8">
+    <row r="87" spans="1:8">
       <c r="A87">
         <v>84</v>
       </c>
@@ -4218,7 +4218,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="88" hidden="1" spans="1:8">
+    <row r="88" spans="1:8">
       <c r="A88">
         <v>85</v>
       </c>
@@ -4241,7 +4241,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="89" hidden="1" spans="1:8">
+    <row r="89" spans="1:8">
       <c r="A89">
         <v>86</v>
       </c>
@@ -4267,7 +4267,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="90" hidden="1" spans="1:8">
+    <row r="90" spans="1:8">
       <c r="A90">
         <v>87</v>
       </c>
@@ -4293,7 +4293,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="91" hidden="1" spans="1:8">
+    <row r="91" spans="1:8">
       <c r="A91">
         <v>88</v>
       </c>
@@ -4319,7 +4319,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="92" hidden="1" spans="1:8">
+    <row r="92" spans="1:8">
       <c r="A92">
         <v>89</v>
       </c>
@@ -4345,7 +4345,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="93" hidden="1" spans="1:8">
+    <row r="93" spans="1:8">
       <c r="A93">
         <v>90</v>
       </c>
@@ -4371,7 +4371,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="94" hidden="1" spans="1:8">
+    <row r="94" spans="1:8">
       <c r="A94">
         <v>91</v>
       </c>
@@ -4397,7 +4397,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="95" hidden="1" spans="1:8">
+    <row r="95" spans="1:8">
       <c r="A95">
         <v>92</v>
       </c>
@@ -4423,7 +4423,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="96" hidden="1" spans="1:8">
+    <row r="96" spans="1:8">
       <c r="A96">
         <v>93</v>
       </c>
@@ -4449,7 +4449,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="97" hidden="1" spans="1:8">
+    <row r="97" spans="1:8">
       <c r="A97">
         <v>94</v>
       </c>
@@ -4475,7 +4475,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="98" hidden="1" spans="1:8">
+    <row r="98" spans="1:8">
       <c r="A98">
         <v>95</v>
       </c>
@@ -4501,7 +4501,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="99" hidden="1" spans="1:8">
+    <row r="99" spans="1:8">
       <c r="A99">
         <v>96</v>
       </c>
@@ -4527,7 +4527,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="100" hidden="1" spans="1:8">
+    <row r="100" spans="1:8">
       <c r="A100">
         <v>97</v>
       </c>
@@ -4553,7 +4553,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="101" hidden="1" spans="1:8">
+    <row r="101" spans="1:8">
       <c r="A101">
         <v>98</v>
       </c>
@@ -4579,7 +4579,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="102" hidden="1" spans="1:8">
+    <row r="102" spans="1:8">
       <c r="A102">
         <v>99</v>
       </c>
@@ -4605,7 +4605,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="103" hidden="1" spans="1:8">
+    <row r="103" spans="1:8">
       <c r="A103">
         <v>100</v>
       </c>
@@ -4631,7 +4631,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="104" hidden="1" spans="1:8">
+    <row r="104" spans="1:8">
       <c r="A104">
         <v>101</v>
       </c>
@@ -4657,7 +4657,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="105" hidden="1" spans="1:8">
+    <row r="105" spans="1:8">
       <c r="A105">
         <v>102</v>
       </c>
@@ -4683,7 +4683,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="106" hidden="1" spans="1:8">
+    <row r="106" spans="1:8">
       <c r="A106">
         <v>103</v>
       </c>
@@ -4709,7 +4709,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="107" hidden="1" spans="1:8">
+    <row r="107" spans="1:8">
       <c r="A107">
         <v>104</v>
       </c>
@@ -4735,7 +4735,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="108" hidden="1" spans="1:8">
+    <row r="108" spans="1:8">
       <c r="A108">
         <v>105</v>
       </c>
@@ -4761,7 +4761,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="109" hidden="1" spans="1:8">
+    <row r="109" spans="1:8">
       <c r="A109">
         <v>106</v>
       </c>
@@ -4787,7 +4787,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="110" hidden="1" spans="1:8">
+    <row r="110" spans="1:8">
       <c r="A110">
         <v>107</v>
       </c>
@@ -4813,7 +4813,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="111" hidden="1" spans="1:8">
+    <row r="111" spans="1:8">
       <c r="A111">
         <v>108</v>
       </c>
@@ -4839,7 +4839,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="112" hidden="1" spans="1:8">
+    <row r="112" spans="1:8">
       <c r="A112">
         <v>109</v>
       </c>
@@ -4865,7 +4865,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="113" hidden="1" spans="1:8">
+    <row r="113" spans="1:8">
       <c r="A113">
         <v>110</v>
       </c>
@@ -4891,7 +4891,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="114" hidden="1" spans="1:8">
+    <row r="114" spans="1:8">
       <c r="A114">
         <v>111</v>
       </c>
@@ -4917,7 +4917,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="115" hidden="1" spans="1:8">
+    <row r="115" spans="1:8">
       <c r="A115">
         <v>112</v>
       </c>
@@ -4943,7 +4943,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="116" hidden="1" spans="1:8">
+    <row r="116" spans="1:8">
       <c r="A116">
         <v>113</v>
       </c>
@@ -4969,7 +4969,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="117" hidden="1" spans="1:8">
+    <row r="117" spans="1:8">
       <c r="A117">
         <v>114</v>
       </c>
@@ -4995,7 +4995,7 @@
         <v>393</v>
       </c>
     </row>
-    <row r="118" hidden="1" spans="1:8">
+    <row r="118" spans="1:8">
       <c r="A118">
         <v>115</v>
       </c>
@@ -5021,7 +5021,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="119" hidden="1" spans="1:8">
+    <row r="119" spans="1:8">
       <c r="A119">
         <v>116</v>
       </c>
@@ -5047,7 +5047,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="120" hidden="1" spans="1:8">
+    <row r="120" spans="1:8">
       <c r="A120">
         <v>117</v>
       </c>
@@ -5070,7 +5070,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="121" hidden="1" spans="1:8">
+    <row r="121" spans="1:8">
       <c r="A121">
         <v>118</v>
       </c>
@@ -5093,7 +5093,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="122" hidden="1" spans="1:8">
+    <row r="122" spans="1:8">
       <c r="A122">
         <v>119</v>
       </c>
@@ -5116,7 +5116,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="123" hidden="1" spans="1:8">
+    <row r="123" spans="1:8">
       <c r="A123">
         <v>120</v>
       </c>
@@ -5139,7 +5139,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="124" hidden="1" spans="1:8">
+    <row r="124" spans="1:8">
       <c r="A124">
         <v>121</v>
       </c>
@@ -5165,7 +5165,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="125" hidden="1" spans="1:8">
+    <row r="125" spans="1:8">
       <c r="A125">
         <v>122</v>
       </c>
@@ -5191,7 +5191,7 @@
         <v>429</v>
       </c>
     </row>
-    <row r="126" hidden="1" spans="1:8">
+    <row r="126" spans="1:8">
       <c r="A126">
         <v>123</v>
       </c>
@@ -5217,7 +5217,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="127" hidden="1" spans="1:8">
+    <row r="127" spans="1:8">
       <c r="A127">
         <v>124</v>
       </c>
@@ -5243,7 +5243,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="128" hidden="1" spans="1:8">
+    <row r="128" spans="1:8">
       <c r="A128">
         <v>125</v>
       </c>
@@ -5266,7 +5266,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="129" hidden="1" spans="1:8">
+    <row r="129" spans="1:8">
       <c r="A129">
         <v>126</v>
       </c>
@@ -5294,75 +5294,6 @@
     </row>
   </sheetData>
   <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H129" etc:filterBottomFollowUsedRange="0">
-    <filterColumn colId="7">
-      <filters>
-        <filter val="官网,http://czzx.gov.cn/"/>
-        <filter val="官网,http://www.chinadaily.com.cn"/>
-        <filter val="官网,http://www.xinhuanet.com"/>
-        <filter val="官网,http://zx.maoming.gov.cn/website/main/jsp/index.jsp"/>
-        <filter val="官网,http://www.jpzx.gov.cn/welcome"/>
-        <filter val="官网,http://www.cnr.cn/;公众号,http://weixin.qq.com/r/Qhy_pnDE5y2YrTTF90lQ;微博,https://weibo.com/u/1683472727;听中国微博,https://weibo.com/u/1867571077"/>
-        <filter val="官网,http://www.people.com.cn/"/>
-        <filter val="官网,http://www.nmgzx.gov.cn/webpage/homepage/index.html"/>
-        <filter val="官网,http://www.workercn.cn"/>
-        <filter val="中国政协网,http://www.cppcc.gov.cn/"/>
-        <filter val="官网,http://www.hainanzx.gov.cn/default.html"/>
-        <filter val="官网,http://www.qstheory.cn"/>
-        <filter val="官网,http://www.shanxizx.gov.cn/"/>
-        <filter val="官网,http://www.tjszx.gov.cn/"/>
-        <filter val="官网,http://www.jieyangzhengxie.gov.cn/"/>
-        <filter val="官网,http://www.81.cn/"/>
-        <filter val="官网,http://www.qhszx.gov.cn/"/>
-        <filter val="官网,http://zx.jiangmen.cn/"/>
-        <filter val="官网,http://www.shszx.gov.cn/"/>
-        <filter val="官网,http://www.sgzxb.gov.cn/"/>
-        <filter val="官网,http://www.cyol.com"/>
-        <filter val="官网,http://www.gdzxb.gov.cn/"/>
-        <filter val="官网,http://www.hljzx.gov.cn/"/>
-        <filter val="官网,http://www.hebzx.gov.cn/"/>
-        <filter val="官网,http://zx.huizhou.gov.cn/"/>
-        <filter val="官网,http://zqzx.gov.cn/index.html"/>
-        <filter val="官网,http://www.chinanews.com"/>
-        <filter val="官网,http://www.ce.cn"/>
-        <filter val="官网,http://www.bjzx.gov.cn/"/>
-        <filter val="官网,http://www.ahzx.gov.cn/"/>
-        <filter val="官网,http://www.ynzx.gov.cn/"/>
-        <filter val="官网,http://www.jlzx.gov.cn/"/>
-        <filter val="官网,http://www.jszx.gov.cn/"/>
-        <filter val="官网,http://www.gxzx.gov.cn/"/>
-        <filter val="官网,http://www.gszx.gov.cn/"/>
-        <filter val="官网,http://www.hnzx.gov.cn/"/>
-        <filter val="官网,http://www.fjzx.gov.cn/"/>
-        <filter val="官网,http://www.fszx.gov.cn/"/>
-        <filter val="官网,http://www.cqzx.gov.cn/"/>
-        <filter val="官网,http://www.sdzx.gov.cn/"/>
-        <filter val="官网,http://www.sczx.gov.cn/"/>
-        <filter val="官网,http://www.zjzx.gov.cn/"/>
-        <filter val="官网,http://www.zhzx.gov.cn/"/>
-        <filter val="官网,http://www.xjzx.gov.cn/"/>
-        <filter val="官网,http://www.szzx.gov.cn/"/>
-        <filter val="官网,http://www.sxzx.gov.cn/"/>
-        <filter val="官网,http://www.swzx.gov.cn/"/>
-        <filter val="官网,http://www.legaldaily.com.cn/"/>
-        <filter val="官网,http://www.mzzx.gov.cn/"/>
-        <filter val="官网,http://www.nxzx.gov.cn/"/>
-        <filter val="官网,http://www.lnzx.gov.cn/"/>
-        <filter val="官网,http://www.farmer.com.cn/"/>
-        <filter val="官网,http://www.gdhyzx.gov.cn/hyzx/index.html"/>
-        <filter val="官网,http://www.stdaily.com"/>
-        <filter val="官网,http://www.jjjcb.cn"/>
-        <filter val="官网,http://www.xizangzx.gov.cn"/>
-        <filter val="官网,http://www.gmw.cn/"/>
-        <filter val="官网,http://zszx.zsnews.cn/"/>
-        <filter val="官网,http://www.gdzjzx.gov.cn/"/>
-        <filter val="官网,http://www.whzx.org.cn/"/>
-        <filter val="官网,http://stzx.shantou.gov.cn/"/>
-        <filter val="官网,http://www.cnwomen.com.cn/"/>
-        <filter val="官网,http://www.cri.cn"/>
-        <filter val="官网,http://dgzx.dg.gov.cn/"/>
-        <filter val="官网,http://zx.yunfu.gov.cn/"/>
-      </filters>
-    </filterColumn>
     <sortState ref="A1:H129">
       <sortCondition ref="A1"/>
     </sortState>

--- a/assets/xlsx/self_links.xlsx
+++ b/assets/xlsx/self_links.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="22680" windowHeight="10410"/>
   </bookViews>
   <sheets>
     <sheet name="links" sheetId="1" r:id="rId1"/>
@@ -764,7 +764,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="424">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="430">
   <si>
     <t>row_seq</t>
   </si>
@@ -1024,18 +1024,18 @@
     <t>http://www.cppcc.gov.cn</t>
   </si>
   <si>
+    <t>中国政府网</t>
+  </si>
+  <si>
+    <t>https://www.gov.cn</t>
+  </si>
+  <si>
     <t>百度百科</t>
   </si>
   <si>
     <t>https://baike.baidu.com/item/%E4%B8%AD%E5%9B%BD%E4%BA%BA%E6%B0%91%E6%94%BF%E6%B2%BB%E5%8D%8F%E5%95%86%E4%BC%9A%E8%AE%AE</t>
   </si>
   <si>
-    <t>中国政府网</t>
-  </si>
-  <si>
-    <t>https://www.gov.cn</t>
-  </si>
-  <si>
     <t>民革</t>
   </si>
   <si>
@@ -1054,6 +1054,12 @@
     <t>https://www.minge.gov.cn</t>
   </si>
   <si>
+    <t>中国政协网</t>
+  </si>
+  <si>
+    <t>http://www.cppcc.gov.cn/</t>
+  </si>
+  <si>
     <t>https://baike.baidu.com/item/%E4%B8%AD%E5%9B%BD%E5%9B%BD%E6%B0%91%E5%85%9A%E9%9D%A9%E5%91%BD%E5%A7%94%E5%91%98%E4%BC%9A</t>
   </si>
   <si>
@@ -1126,6 +1132,9 @@
     <t>https://www.ngd.org.cn</t>
   </si>
   <si>
+    <t>https://baike.baidu.com/item/%E4%B8%AD%E5%9B%BD%E5%86%9C%E5%B7%A5%E6%B0%91%E4%B8%BB%E5%85%9A</t>
+  </si>
+  <si>
     <t>致公党</t>
   </si>
   <si>
@@ -1141,6 +1150,9 @@
     <t>https://www.zg.org.cn</t>
   </si>
   <si>
+    <t>https://baike.baidu.com/item/%E4%B8%AD%E5%9B%BD%E8%87%B4%E5%85%AC%E5%85%9A</t>
+  </si>
+  <si>
     <t>九三学社</t>
   </si>
   <si>
@@ -1153,6 +1165,9 @@
     <t>https://www.93.gov.cn</t>
   </si>
   <si>
+    <t>https://baike.baidu.com/item/%E4%B9%9D%E4%B8%89%E5%AD%A6%E7%A4%BE</t>
+  </si>
+  <si>
     <t>台盟</t>
   </si>
   <si>
@@ -1166,6 +1181,9 @@
   </si>
   <si>
     <t>https://www.taimeng.org.cn</t>
+  </si>
+  <si>
+    <t>https://baike.baidu.com/item/%E5%8F%B0%E6%B9%BE%E6%B0%91%E4%B8%BB%E8%87%AA%E6%B2%BB%E5%90%8C%E7%9B%9F</t>
   </si>
   <si>
     <t>北京市政协</t>
@@ -2654,8 +2672,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3007,18 +3028,12 @@
   <cols>
     <col min="4" max="4" width="4.625" customWidth="1"/>
     <col min="5" max="5" width="13.375" customWidth="1"/>
-    <col min="8" max="8" width="12.5" customWidth="1"/>
-    <col min="9" max="9" width="11.25" customWidth="1"/>
-    <col min="10" max="10" width="10.5" customWidth="1"/>
+    <col min="8" max="11" width="4" customWidth="1"/>
+    <col min="12" max="12" width="19.875" customWidth="1"/>
     <col min="15" max="15" width="17" customWidth="1"/>
     <col min="16" max="16" width="7.5" customWidth="1"/>
-    <col min="17" max="17" width="15.5" customWidth="1"/>
-    <col min="18" max="18" width="25.375" customWidth="1"/>
-    <col min="19" max="19" width="12.75" customWidth="1"/>
-    <col min="20" max="20" width="15.5" customWidth="1"/>
-    <col min="21" max="22" width="13.75" customWidth="1"/>
-    <col min="27" max="27" width="18.875" customWidth="1"/>
-    <col min="45" max="45" width="16" customWidth="1"/>
+    <col min="17" max="70" width="2.25" hidden="1" customWidth="1" outlineLevel="1"/>
+    <col min="71" max="71" width="9" collapsed="1"/>
     <col min="72" max="72" width="9" customWidth="1"/>
     <col min="76" max="76" width="14.875" customWidth="1"/>
     <col min="77" max="77" width="13.5" customWidth="1"/>
@@ -3341,10 +3356,16 @@
         <v>95</v>
       </c>
       <c r="BS3" t="s">
-        <v>86</v>
-      </c>
-      <c r="BT3" t="s">
         <v>96</v>
+      </c>
+      <c r="BT3" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>88</v>
+      </c>
+      <c r="BV3" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -3352,31 +3373,37 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H4" t="s">
         <v>93</v>
       </c>
       <c r="L4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="M4" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="BS4" t="s">
-        <v>86</v>
-      </c>
-      <c r="BT4" t="s">
-        <v>102</v>
+        <v>96</v>
+      </c>
+      <c r="BT4" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="BU4" t="s">
+        <v>88</v>
+      </c>
+      <c r="BV4" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -3384,31 +3411,37 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F5" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="H5" t="s">
         <v>93</v>
       </c>
       <c r="L5" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="M5" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="BS5" t="s">
-        <v>86</v>
-      </c>
-      <c r="BT5" t="s">
-        <v>108</v>
+        <v>96</v>
+      </c>
+      <c r="BT5" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>88</v>
+      </c>
+      <c r="BV5" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -3416,31 +3449,37 @@
         <v>4</v>
       </c>
       <c r="C6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D6">
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H6" t="s">
         <v>93</v>
       </c>
       <c r="L6" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="M6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="BS6" t="s">
-        <v>86</v>
-      </c>
-      <c r="BT6" t="s">
-        <v>114</v>
+        <v>96</v>
+      </c>
+      <c r="BT6" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>88</v>
+      </c>
+      <c r="BV6" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -3448,25 +3487,37 @@
         <v>5</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="D7">
         <v>1</v>
       </c>
       <c r="E7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="F7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H7" t="s">
         <v>93</v>
       </c>
       <c r="L7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="M7" t="s">
-        <v>119</v>
+        <v>121</v>
+      </c>
+      <c r="BS7" t="s">
+        <v>96</v>
+      </c>
+      <c r="BT7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="BU7" t="s">
+        <v>88</v>
+      </c>
+      <c r="BV7" s="1" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -3474,25 +3525,37 @@
         <v>6</v>
       </c>
       <c r="C8" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="D8">
         <v>1</v>
       </c>
       <c r="E8" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="F8" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="H8" t="s">
         <v>93</v>
       </c>
       <c r="L8" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s">
-        <v>124</v>
+        <v>127</v>
+      </c>
+      <c r="BS8" t="s">
+        <v>96</v>
+      </c>
+      <c r="BT8" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="BU8" t="s">
+        <v>88</v>
+      </c>
+      <c r="BV8" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -3500,25 +3563,37 @@
         <v>7</v>
       </c>
       <c r="C9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D9">
         <v>1</v>
       </c>
       <c r="E9" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="H9" t="s">
         <v>93</v>
       </c>
       <c r="L9" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="M9" t="s">
-        <v>128</v>
+        <v>132</v>
+      </c>
+      <c r="BS9" t="s">
+        <v>96</v>
+      </c>
+      <c r="BT9" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="BU9" t="s">
+        <v>88</v>
+      </c>
+      <c r="BV9" s="1" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3526,25 +3601,37 @@
         <v>8</v>
       </c>
       <c r="C10" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="D10">
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="F10" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="H10" t="s">
         <v>93</v>
       </c>
       <c r="L10" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="M10" t="s">
-        <v>133</v>
+        <v>138</v>
+      </c>
+      <c r="BS10" t="s">
+        <v>96</v>
+      </c>
+      <c r="BT10" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="BU10" t="s">
+        <v>88</v>
+      </c>
+      <c r="BV10" s="1" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3558,19 +3645,19 @@
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="F11" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="H11" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="L11" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="M11" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3584,19 +3671,19 @@
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="F12" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H12" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="L12" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="M12" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3610,19 +3697,19 @@
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F13" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="H13" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="L13" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="M13" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -3636,19 +3723,19 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="F14" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="H14" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="L14" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="M14" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -3662,22 +3749,22 @@
         <v>1</v>
       </c>
       <c r="E15" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="F15" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="G15" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="H15" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="L15" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="M15" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -3691,19 +3778,19 @@
         <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="F16" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="H16" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="L16" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="M16" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
     </row>
     <row r="17" spans="1:13">
@@ -3717,19 +3804,19 @@
         <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="F17" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="H17" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="L17" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="M17" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
     </row>
     <row r="18" spans="1:13">
@@ -3743,19 +3830,19 @@
         <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="F18" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="H18" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="L18" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="M18" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
     </row>
     <row r="19" spans="1:13">
@@ -3769,19 +3856,19 @@
         <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="F19" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="H19" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="L19" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="M19" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
     </row>
     <row r="20" spans="1:13">
@@ -3795,19 +3882,19 @@
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F20" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="H20" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="L20" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="M20" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
     </row>
     <row r="21" spans="1:13">
@@ -3821,19 +3908,19 @@
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="F21" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="H21" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="L21" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="M21" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:13">
@@ -3847,19 +3934,19 @@
         <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="F22" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="H22" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="L22" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="M22" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23" spans="1:13">
@@ -3873,19 +3960,19 @@
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F23" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="H23" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="L23" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="M23" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
     </row>
     <row r="24" spans="1:13">
@@ -3899,19 +3986,19 @@
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="F24" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="H24" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="L24" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="M24" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="25" spans="1:13">
@@ -3925,19 +4012,19 @@
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="F25" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="H25" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="L25" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="M25" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -3951,22 +4038,22 @@
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F26" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="G26" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="H26" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="L26" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="M26" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -3980,22 +4067,22 @@
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="F27" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="G27" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="H27" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="L27" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="M27" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
     </row>
     <row r="28" spans="1:13">
@@ -4009,19 +4096,19 @@
         <v>1</v>
       </c>
       <c r="E28" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F28" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="H28" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="L28" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="M28" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
     </row>
     <row r="29" spans="1:13">
@@ -4035,19 +4122,19 @@
         <v>1</v>
       </c>
       <c r="E29" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="F29" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="H29" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="L29" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="M29" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
     </row>
     <row r="30" spans="1:13">
@@ -4061,19 +4148,19 @@
         <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="F30" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="H30" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="L30" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="M30" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
     </row>
     <row r="31" spans="1:13">
@@ -4087,19 +4174,19 @@
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="F31" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="H31" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="L31" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="M31" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -4113,19 +4200,19 @@
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F32" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="H32" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="L32" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="M32" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
     </row>
     <row r="33" spans="1:13">
@@ -4139,19 +4226,19 @@
         <v>1</v>
       </c>
       <c r="E33" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="F33" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="H33" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="L33" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="M33" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="34" spans="1:13">
@@ -4165,19 +4252,19 @@
         <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="F34" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="H34" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="L34" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="M34" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
     </row>
     <row r="35" spans="1:13">
@@ -4191,19 +4278,19 @@
         <v>1</v>
       </c>
       <c r="E35" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="F35" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="H35" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="L35" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="M35" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
     </row>
     <row r="36" spans="1:13">
@@ -4217,19 +4304,19 @@
         <v>1</v>
       </c>
       <c r="E36" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="F36" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="H36" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="L36" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="M36" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
     </row>
     <row r="37" spans="1:13">
@@ -4243,19 +4330,19 @@
         <v>1</v>
       </c>
       <c r="E37" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="F37" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="H37" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="L37" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="M37" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
     </row>
     <row r="38" spans="1:13">
@@ -4269,19 +4356,19 @@
         <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="F38" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="H38" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="L38" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="M38" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
     </row>
     <row r="39" spans="1:13">
@@ -4295,19 +4382,19 @@
         <v>1</v>
       </c>
       <c r="E39" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="F39" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="H39" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="L39" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="M39" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
     </row>
     <row r="40" spans="1:13">
@@ -4321,19 +4408,19 @@
         <v>1</v>
       </c>
       <c r="E40" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="F40" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="H40" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="L40" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="M40" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
     </row>
     <row r="41" spans="1:13">
@@ -4347,19 +4434,19 @@
         <v>1</v>
       </c>
       <c r="E41" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="F41" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="H41" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="L41" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="M41" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
     </row>
     <row r="42" spans="1:13">
@@ -4373,22 +4460,22 @@
         <v>1</v>
       </c>
       <c r="E42" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="F42" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="G42" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="H42" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="L42" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="M42" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
     </row>
     <row r="43" spans="1:13">
@@ -4402,19 +4489,19 @@
         <v>1</v>
       </c>
       <c r="E43" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="F43" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="H43" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="L43" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="M43" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:13">
@@ -4428,19 +4515,19 @@
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="F44" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="H44" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="L44" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="M44" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
     </row>
     <row r="45" spans="1:13">
@@ -4454,19 +4541,19 @@
         <v>1</v>
       </c>
       <c r="E45" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="F45" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="H45" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="L45" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="M45" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
     </row>
     <row r="46" spans="1:13">
@@ -4480,22 +4567,22 @@
         <v>1</v>
       </c>
       <c r="E46" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="F46" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="G46" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="H46" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="L46" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="M46" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
     </row>
     <row r="47" spans="1:13">
@@ -4509,19 +4596,19 @@
         <v>1</v>
       </c>
       <c r="E47" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="F47" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="H47" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="L47" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="M47" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
     </row>
     <row r="48" spans="1:13">
@@ -4535,19 +4622,19 @@
         <v>1</v>
       </c>
       <c r="E48" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="F48" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="H48" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="L48" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="M48" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
     </row>
     <row r="49" spans="1:13">
@@ -4561,19 +4648,19 @@
         <v>1</v>
       </c>
       <c r="E49" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="F49" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="H49" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="L49" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="M49" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
     </row>
     <row r="50" spans="1:13">
@@ -4587,19 +4674,19 @@
         <v>1</v>
       </c>
       <c r="E50" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="F50" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="H50" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="L50" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="M50" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
     </row>
     <row r="51" spans="1:13">
@@ -4613,19 +4700,19 @@
         <v>1</v>
       </c>
       <c r="E51" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="F51" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="H51" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="L51" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="M51" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
     </row>
     <row r="52" spans="1:13">
@@ -4639,19 +4726,19 @@
         <v>1</v>
       </c>
       <c r="E52" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="F52" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="H52" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="L52" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="M52" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
     </row>
     <row r="53" spans="1:13">
@@ -4665,19 +4752,19 @@
         <v>1</v>
       </c>
       <c r="E53" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="F53" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="H53" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="L53" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="M53" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
     </row>
     <row r="54" spans="1:13">
@@ -4691,19 +4778,19 @@
         <v>1</v>
       </c>
       <c r="E54" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="F54" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="H54" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="L54" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="M54" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
     </row>
     <row r="55" spans="1:13">
@@ -4717,19 +4804,19 @@
         <v>1</v>
       </c>
       <c r="E55" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="F55" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="H55" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="L55" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="M55" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
     </row>
     <row r="56" spans="1:13">
@@ -4743,19 +4830,19 @@
         <v>1</v>
       </c>
       <c r="E56" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="F56" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="H56" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="L56" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="M56" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
     </row>
     <row r="57" spans="1:13">
@@ -4769,22 +4856,22 @@
         <v>1</v>
       </c>
       <c r="E57" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="F57" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="G57" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="H57" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="L57" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="M57" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
     </row>
     <row r="58" spans="1:13">
@@ -4798,19 +4885,19 @@
         <v>1</v>
       </c>
       <c r="E58" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="F58" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H58" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="L58" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="M58" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
     </row>
     <row r="59" spans="1:13">
@@ -4824,19 +4911,19 @@
         <v>1</v>
       </c>
       <c r="E59" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="F59" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="H59" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="L59" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="M59" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
     </row>
     <row r="60" spans="1:13">
@@ -4850,19 +4937,19 @@
         <v>1</v>
       </c>
       <c r="E60" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="F60" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="H60" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="L60" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="M60" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
     </row>
     <row r="61" spans="1:13">
@@ -4876,19 +4963,19 @@
         <v>1</v>
       </c>
       <c r="E61" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="F61" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="H61" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="L61" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="M61" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
     </row>
     <row r="62" spans="1:13">
@@ -4902,19 +4989,19 @@
         <v>1</v>
       </c>
       <c r="E62" t="s">
-        <v>395</v>
+        <v>401</v>
       </c>
       <c r="F62" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="H62" t="s">
-        <v>397</v>
+        <v>403</v>
       </c>
       <c r="L62" t="s">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="M62" t="s">
-        <v>399</v>
+        <v>405</v>
       </c>
     </row>
     <row r="63" spans="1:13">
@@ -4928,19 +5015,19 @@
         <v>1</v>
       </c>
       <c r="E63" t="s">
-        <v>400</v>
+        <v>406</v>
       </c>
       <c r="F63" t="s">
-        <v>401</v>
+        <v>407</v>
       </c>
       <c r="H63" t="s">
-        <v>402</v>
+        <v>408</v>
       </c>
       <c r="L63" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="M63" t="s">
-        <v>404</v>
+        <v>410</v>
       </c>
     </row>
     <row r="64" spans="1:13">
@@ -4954,19 +5041,19 @@
         <v>1</v>
       </c>
       <c r="E64" t="s">
-        <v>405</v>
+        <v>411</v>
       </c>
       <c r="F64" t="s">
-        <v>406</v>
+        <v>412</v>
       </c>
       <c r="H64" t="s">
-        <v>407</v>
+        <v>413</v>
       </c>
       <c r="L64" t="s">
-        <v>408</v>
+        <v>414</v>
       </c>
       <c r="M64" t="s">
-        <v>409</v>
+        <v>415</v>
       </c>
     </row>
     <row r="65" spans="1:72">
@@ -4974,37 +5061,37 @@
         <v>9023</v>
       </c>
       <c r="C65" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="D65">
         <v>1</v>
       </c>
       <c r="E65" t="s">
-        <v>411</v>
+        <v>417</v>
       </c>
       <c r="F65" t="s">
-        <v>412</v>
+        <v>418</v>
       </c>
       <c r="G65" t="s">
-        <v>413</v>
+        <v>419</v>
       </c>
       <c r="L65" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="M65" t="s">
-        <v>415</v>
+        <v>421</v>
       </c>
       <c r="R65" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="S65" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
       <c r="BS65" t="s">
-        <v>416</v>
+        <v>422</v>
       </c>
       <c r="BT65" t="s">
-        <v>417</v>
+        <v>423</v>
       </c>
     </row>
     <row r="66" spans="1:72">
@@ -5012,37 +5099,37 @@
         <v>9024</v>
       </c>
       <c r="C66" t="s">
-        <v>410</v>
+        <v>416</v>
       </c>
       <c r="D66">
         <v>1</v>
       </c>
       <c r="E66" t="s">
-        <v>418</v>
+        <v>424</v>
       </c>
       <c r="F66" t="s">
-        <v>419</v>
+        <v>425</v>
       </c>
       <c r="G66" t="s">
+        <v>426</v>
+      </c>
+      <c r="L66" t="s">
         <v>420</v>
       </c>
-      <c r="L66" t="s">
-        <v>414</v>
-      </c>
       <c r="M66" t="s">
-        <v>421</v>
+        <v>427</v>
       </c>
       <c r="R66" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="S66" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="BS66" t="s">
-        <v>422</v>
+        <v>428</v>
       </c>
       <c r="BT66" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
     </row>
   </sheetData>
@@ -5050,6 +5137,19 @@
     <hyperlink ref="G42" r:id="rId3" display="https://www.gzzx.gov.cn/images/iconcf134.ico"/>
     <hyperlink ref="G46" r:id="rId4" display="http://www.jpzx.gov.cn/favicon.ico"/>
     <hyperlink ref="G57" r:id="rId5" display="https://www.google.com/s2/favicons?domain=http://www.gdzjzx.gov.cn/"/>
+    <hyperlink ref="BT3" r:id="rId6" display="http://www.cppcc.gov.cn/"/>
+    <hyperlink ref="BT4" r:id="rId6" display="http://www.cppcc.gov.cn/"/>
+    <hyperlink ref="BT5" r:id="rId6" display="http://www.cppcc.gov.cn/"/>
+    <hyperlink ref="BT6" r:id="rId6" display="http://www.cppcc.gov.cn/"/>
+    <hyperlink ref="BT7" r:id="rId6" display="http://www.cppcc.gov.cn/"/>
+    <hyperlink ref="BT8" r:id="rId6" display="http://www.cppcc.gov.cn/"/>
+    <hyperlink ref="BT9" r:id="rId6" display="http://www.cppcc.gov.cn/"/>
+    <hyperlink ref="BT10" r:id="rId6" display="http://www.cppcc.gov.cn/"/>
+    <hyperlink ref="BV6" r:id="rId7" display="https://baike.baidu.com/item/%E4%B8%AD%E5%9B%BD%E6%B0%91%E4%B8%BB%E4%BF%83%E8%BF%9B%E4%BC%9A"/>
+    <hyperlink ref="BV7" r:id="rId8" display="https://baike.baidu.com/item/%E4%B8%AD%E5%9B%BD%E5%86%9C%E5%B7%A5%E6%B0%91%E4%B8%BB%E5%85%9A"/>
+    <hyperlink ref="BV8" r:id="rId9" display="https://baike.baidu.com/item/%E4%B8%AD%E5%9B%BD%E8%87%B4%E5%85%AC%E5%85%9A"/>
+    <hyperlink ref="BV9" r:id="rId10" display="https://baike.baidu.com/item/%E4%B9%9D%E4%B8%89%E5%AD%A6%E7%A4%BE"/>
+    <hyperlink ref="BV10" r:id="rId11" display="https://baike.baidu.com/item/%E5%8F%B0%E6%B9%BE%E6%B0%91%E4%B8%BB%E8%87%AA%E6%B2%BB%E5%90%8C%E7%9B%9F"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>

--- a/assets/xlsx/self_links.xlsx
+++ b/assets/xlsx/self_links.xlsx
@@ -4,11 +4,14 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22680" windowHeight="10410"/>
+    <workbookView windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="links" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">links!$A$1:$AE$66</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -44,18 +47,6 @@
         </r>
       </text>
     </comment>
-    <comment ref="B1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>分类键。该卡片所属分类标识（如 政协/民革/全国/直辖市）。</t>
-        </r>
-      </text>
-    </comment>
     <comment ref="C1" authorId="0">
       <text>
         <r>
@@ -76,7 +67,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>卡片版式。取值 1/2/3，表示卡片展示版式（非数据类型，候选未单列，建议保留）。</t>
+          <t>分类键。该卡片所属分类标识（如 政协/民革/全国/直辖市）。</t>
         </r>
       </text>
     </comment>
@@ -88,7 +79,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>卡片标题。可能是网站名/机构名/企业名/人名/书名/电影名甚至一条意见。</t>
+          <t>卡片版式。取值 1/2/3，表示卡片展示版式（非数据类型，候选未单列，建议保留）。</t>
         </r>
       </text>
     </comment>
@@ -100,11 +91,23 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
+          <t>卡片标题。可能是网站名/机构名/企业名/人名/书名/电影名甚至一条意见。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
           <t>卡片描述。对卡片内容的说明文字。</t>
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="H1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -123,7 +126,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="0">
+    <comment ref="I1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -135,7 +138,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="0">
+    <comment ref="J1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -147,7 +150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="0">
+    <comment ref="K1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -156,18 +159,6 @@
             <charset val="134"/>
           </rPr>
           <t>卡片排序权重。数字越小越靠前；留空按 row_seq。圆桌 11 棒提议，原 32 列曾删，现补回。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="K1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 个链接的显示名。</t>
         </r>
       </text>
     </comment>
@@ -203,7 +194,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>第 1 链接描述。</t>
+          <t>第 1 个链接的显示名。</t>
         </r>
       </text>
     </comment>
@@ -215,7 +206,19 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>第 1 链接级 favicon（覆盖卡片级 card_media）。</t>
+          <t>第 1 个链接的地址 URL。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="P1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>第 1 个链接的显示名。</t>
         </r>
       </text>
     </comment>
@@ -227,7 +230,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>第 1 个链接的显示名。</t>
+          <t>第 1 个链接的地址 URL。</t>
         </r>
       </text>
     </comment>
@@ -263,7 +266,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>第 1 链接描述。</t>
+          <t>第 1 个链接的显示名。</t>
         </r>
       </text>
     </comment>
@@ -275,7 +278,19 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>第 1 链接级 favicon（覆盖卡片级 card_media）。</t>
+          <t>第 1 个链接的地址 URL。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="V1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>第 1 个链接的显示名。</t>
         </r>
       </text>
     </comment>
@@ -287,7 +302,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>第 1 个链接的显示名。</t>
+          <t>第 1 个链接的地址 URL。</t>
         </r>
       </text>
     </comment>
@@ -323,7 +338,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>第 1 链接描述。</t>
+          <t>第 1 个链接的显示名。</t>
         </r>
       </text>
     </comment>
@@ -335,7 +350,19 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>第 1 链接级 favicon（覆盖卡片级 card_media）。</t>
+          <t>第 1 个链接的地址 URL。</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AB1" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>第 1 个链接的显示名。</t>
         </r>
       </text>
     </comment>
@@ -347,7 +374,7 @@
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>第 1 个链接的显示名。</t>
+          <t>第 1 个链接的地址 URL。</t>
         </r>
       </text>
     </comment>
@@ -375,400 +402,19 @@
         </r>
       </text>
     </comment>
-    <comment ref="AF1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 链接描述。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AG1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 链接级 favicon（覆盖卡片级 card_media）。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AI1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 个链接的显示名。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AJ1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 个链接的显示名。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AK1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 个链接的地址 URL。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AL1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 链接描述。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AM1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 链接级 favicon（覆盖卡片级 card_media）。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AO1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 个链接的显示名。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AP1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 个链接的显示名。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AQ1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 个链接的地址 URL。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AR1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 链接描述。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AS1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 链接级 favicon（覆盖卡片级 card_media）。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AU1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 个链接的显示名。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AV1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 个链接的显示名。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AW1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 个链接的地址 URL。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AX1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 链接描述。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AY1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 链接级 favicon（覆盖卡片级 card_media）。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="BA1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 个链接的显示名。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="BB1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 个链接的显示名。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="BC1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 个链接的地址 URL。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="BD1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 链接描述。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="BE1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 链接级 favicon（覆盖卡片级 card_media）。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="BG1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 个链接的显示名。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="BH1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 个链接的显示名。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="BI1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 个链接的地址 URL。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="BJ1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 链接描述。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="BK1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 链接级 favicon（覆盖卡片级 card_media）。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="BM1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 个链接的显示名。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="BN1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 个链接的显示名。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="BO1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 个链接的地址 URL。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="BP1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 链接描述。</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="BQ1" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="宋体"/>
-            <charset val="134"/>
-          </rPr>
-          <t>第 1 链接级 favicon（覆盖卡片级 card_media）。</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="367">
   <si>
     <t>row_seq</t>
   </si>
   <si>
+    <t>dir_path</t>
+  </si>
+  <si>
     <t>cat_id</t>
   </si>
   <si>
@@ -796,216 +442,66 @@
     <t>card_order</t>
   </si>
   <si>
-    <t>link_1_id</t>
-  </si>
-  <si>
     <t>link_1_name</t>
   </si>
   <si>
     <t>link_1_url</t>
   </si>
   <si>
-    <t>link_1_desc</t>
-  </si>
-  <si>
-    <t>link_1_media</t>
-  </si>
-  <si>
-    <t>link_1_enabled</t>
-  </si>
-  <si>
-    <t>link_2_id</t>
-  </si>
-  <si>
     <t>link_2_name</t>
   </si>
   <si>
     <t>link_2_url</t>
   </si>
   <si>
-    <t>link_2_desc</t>
-  </si>
-  <si>
-    <t>link_2_media</t>
-  </si>
-  <si>
-    <t>link_2_enabled</t>
-  </si>
-  <si>
-    <t>link_3_id</t>
-  </si>
-  <si>
     <t>link_3_name</t>
   </si>
   <si>
     <t>link_3_url</t>
   </si>
   <si>
-    <t>link_3_desc</t>
-  </si>
-  <si>
-    <t>link_3_media</t>
-  </si>
-  <si>
-    <t>link_3_enabled</t>
-  </si>
-  <si>
-    <t>link_4_id</t>
-  </si>
-  <si>
     <t>link_4_name</t>
   </si>
   <si>
     <t>link_4_url</t>
   </si>
   <si>
-    <t>link_4_desc</t>
-  </si>
-  <si>
-    <t>link_4_media</t>
-  </si>
-  <si>
-    <t>link_4_enabled</t>
-  </si>
-  <si>
-    <t>link_5_id</t>
-  </si>
-  <si>
     <t>link_5_name</t>
   </si>
   <si>
     <t>link_5_url</t>
   </si>
   <si>
-    <t>link_5_desc</t>
-  </si>
-  <si>
-    <t>link_5_media</t>
-  </si>
-  <si>
-    <t>link_5_enabled</t>
-  </si>
-  <si>
-    <t>link_6_id</t>
-  </si>
-  <si>
     <t>link_6_name</t>
   </si>
   <si>
     <t>link_6_url</t>
   </si>
   <si>
-    <t>link_6_desc</t>
-  </si>
-  <si>
-    <t>link_6_media</t>
-  </si>
-  <si>
-    <t>link_6_enabled</t>
-  </si>
-  <si>
-    <t>link_7_id</t>
-  </si>
-  <si>
     <t>link_7_name</t>
   </si>
   <si>
     <t>link_7_url</t>
   </si>
   <si>
-    <t>link_7_desc</t>
-  </si>
-  <si>
-    <t>link_7_media</t>
-  </si>
-  <si>
-    <t>link_7_enabled</t>
-  </si>
-  <si>
-    <t>link_8_id</t>
-  </si>
-  <si>
     <t>link_8_name</t>
   </si>
   <si>
     <t>link_8_url</t>
   </si>
   <si>
-    <t>link_8_desc</t>
-  </si>
-  <si>
-    <t>link_8_media</t>
-  </si>
-  <si>
-    <t>link_8_enabled</t>
-  </si>
-  <si>
-    <t>link_9_id</t>
-  </si>
-  <si>
     <t>link_9_name</t>
   </si>
   <si>
     <t>link_9_url</t>
   </si>
   <si>
-    <t>link_9_desc</t>
-  </si>
-  <si>
-    <t>link_9_media</t>
-  </si>
-  <si>
-    <t>link_9_enabled</t>
-  </si>
-  <si>
-    <t>link_10_id</t>
-  </si>
-  <si>
     <t>link_10_name</t>
   </si>
   <si>
     <t>link_10_url</t>
   </si>
   <si>
-    <t>link_10_desc</t>
-  </si>
-  <si>
-    <t>link_10_media</t>
-  </si>
-  <si>
-    <t>link_10_enabled</t>
-  </si>
-  <si>
-    <t>source_1_name</t>
-  </si>
-  <si>
-    <t>source_1_url</t>
-  </si>
-  <si>
-    <t>source_2_name</t>
-  </si>
-  <si>
-    <t>source_2_url</t>
-  </si>
-  <si>
-    <t>source_3_name</t>
-  </si>
-  <si>
-    <t>source_3_url</t>
-  </si>
-  <si>
-    <t>source_4_name</t>
-  </si>
-  <si>
-    <t>source_4_url</t>
-  </si>
-  <si>
-    <t>source_5_name</t>
-  </si>
-  <si>
-    <t>source_5_url</t>
-  </si>
-  <si>
     <t>政协</t>
   </si>
   <si>
@@ -1024,18 +520,6 @@
     <t>http://www.cppcc.gov.cn</t>
   </si>
   <si>
-    <t>中国政府网</t>
-  </si>
-  <si>
-    <t>https://www.gov.cn</t>
-  </si>
-  <si>
-    <t>百度百科</t>
-  </si>
-  <si>
-    <t>https://baike.baidu.com/item/%E4%B8%AD%E5%9B%BD%E4%BA%BA%E6%B0%91%E6%94%BF%E6%B2%BB%E5%8D%8F%E5%95%86%E4%BC%9A%E8%AE%AE</t>
-  </si>
-  <si>
     <t>民革</t>
   </si>
   <si>
@@ -1054,15 +538,6 @@
     <t>https://www.minge.gov.cn</t>
   </si>
   <si>
-    <t>中国政协网</t>
-  </si>
-  <si>
-    <t>http://www.cppcc.gov.cn/</t>
-  </si>
-  <si>
-    <t>https://baike.baidu.com/item/%E4%B8%AD%E5%9B%BD%E5%9B%BD%E6%B0%91%E5%85%9A%E9%9D%A9%E5%91%BD%E5%A7%94%E5%91%98%E4%BC%9A</t>
-  </si>
-  <si>
     <t>民盟</t>
   </si>
   <si>
@@ -1078,9 +553,6 @@
     <t>https://www.dem-league.org.cn</t>
   </si>
   <si>
-    <t>https://baike.baidu.com/item/%E4%B8%AD%E5%9B%BD%E6%B0%91%E4%B8%BB%E5%90%8C%E7%9B%9F</t>
-  </si>
-  <si>
     <t>民建</t>
   </si>
   <si>
@@ -1096,9 +568,6 @@
     <t>http://www.cndca.org.cn</t>
   </si>
   <si>
-    <t>https://baike.baidu.com/item/%E4%B8%AD%E5%9B%BD%E6%B0%91%E4%B8%BB%E5%BB%BA%E5%9B%BD%E4%BC%9A</t>
-  </si>
-  <si>
     <t>民进</t>
   </si>
   <si>
@@ -1114,9 +583,6 @@
     <t>https://www.mj.org.cn</t>
   </si>
   <si>
-    <t>https://baike.baidu.com/item/%E4%B8%AD%E5%9B%BD%E6%B0%91%E4%B8%BB%E4%BF%83%E8%BF%9B%E4%BC%9A</t>
-  </si>
-  <si>
     <t>农工党</t>
   </si>
   <si>
@@ -1132,9 +598,6 @@
     <t>https://www.ngd.org.cn</t>
   </si>
   <si>
-    <t>https://baike.baidu.com/item/%E4%B8%AD%E5%9B%BD%E5%86%9C%E5%B7%A5%E6%B0%91%E4%B8%BB%E5%85%9A</t>
-  </si>
-  <si>
     <t>致公党</t>
   </si>
   <si>
@@ -1150,9 +613,6 @@
     <t>https://www.zg.org.cn</t>
   </si>
   <si>
-    <t>https://baike.baidu.com/item/%E4%B8%AD%E5%9B%BD%E8%87%B4%E5%85%AC%E5%85%9A</t>
-  </si>
-  <si>
     <t>九三学社</t>
   </si>
   <si>
@@ -1165,9 +625,6 @@
     <t>https://www.93.gov.cn</t>
   </si>
   <si>
-    <t>https://baike.baidu.com/item/%E4%B9%9D%E4%B8%89%E5%AD%A6%E7%A4%BE</t>
-  </si>
-  <si>
     <t>台盟</t>
   </si>
   <si>
@@ -1183,9 +640,6 @@
     <t>https://www.taimeng.org.cn</t>
   </si>
   <si>
-    <t>https://baike.baidu.com/item/%E5%8F%B0%E6%B9%BE%E6%B0%91%E4%B8%BB%E8%87%AA%E6%B2%BB%E5%90%8C%E7%9B%9F</t>
-  </si>
-  <si>
     <t>北京市政协</t>
   </si>
   <si>
@@ -1669,7 +1123,7 @@
     <t>https://www.gzzx.gov.cn/images/iconcf134.ico</t>
   </si>
   <si>
-    <t>广东省,广州市</t>
+    <t>广东省,广州市,副省级市政协</t>
   </si>
   <si>
     <t>访问官网 - www.gzzx.gov.cn</t>
@@ -1684,7 +1138,7 @@
     <t>中国人民政治协商会议深圳市委员会官方网站。提供政协动态、会议提案、委员履职等信息。本站为第三方导航，与官方无隶属关系，不对跳转后内容负责。</t>
   </si>
   <si>
-    <t>广东省,深圳市</t>
+    <t>广东省,深圳市,副省级市政协</t>
   </si>
   <si>
     <t>访问官网 - www.szzx.gov.cn</t>
@@ -1732,7 +1186,7 @@
     <t>http://www.jpzx.gov.cn/favicon.ico</t>
   </si>
   <si>
-    <t>广东省,汕头市金平区</t>
+    <t>广东省,汕头市金平区,市辖区政协</t>
   </si>
   <si>
     <t>访问官网 - www.jpzx.gov.cn</t>
@@ -1990,7 +1444,7 @@
     <t>中国人民政治协商会议哈尔滨市委员会官方网站。提供政协动态、会议提案、委员履职等信息。本站为第三方导航，与官方无隶属关系，不对跳转后内容负责。</t>
   </si>
   <si>
-    <t>黑龙江省,哈尔滨市</t>
+    <t>黑龙江省,哈尔滨市,副省级市政协</t>
   </si>
   <si>
     <t>访问官网 - www.hrbzx.gov.cn</t>
@@ -2005,7 +1459,7 @@
     <t>中国人民政治协商会议武汉市委员会官方网站。提供政协动态、会议提案、委员履职等信息。本站为第三方导航，与官方无隶属关系，不对跳转后内容负责。</t>
   </si>
   <si>
-    <t>湖北省,武汉市</t>
+    <t>湖北省,武汉市,副省级市政协</t>
   </si>
   <si>
     <t>访问官网 - www.whzx.org.cn</t>
@@ -2679,55 +2133,55 @@
     </xf>
   </cellXfs>
   <cellStyles count="49">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+    <cellStyle name="Currency" xfId="2" builtinId="4"/>
+    <cellStyle name="Percent" xfId="3" builtinId="5"/>
+    <cellStyle name="Comma [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Currency [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Link" xfId="6" builtinId="8"/>
+    <cellStyle name="Followed Hyperlink" xfId="7" builtinId="9"/>
+    <cellStyle name="Note" xfId="8" builtinId="10"/>
+    <cellStyle name="Warning Text" xfId="9" builtinId="11"/>
+    <cellStyle name="Title" xfId="10" builtinId="15"/>
+    <cellStyle name="Explanatory Text" xfId="11" builtinId="53"/>
+    <cellStyle name="Heading 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Heading 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Heading 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Heading 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Input" xfId="16" builtinId="20"/>
+    <cellStyle name="Output" xfId="17" builtinId="21"/>
+    <cellStyle name="Calculation" xfId="18" builtinId="22"/>
+    <cellStyle name="Check Cell" xfId="19" builtinId="23"/>
+    <cellStyle name="Linked Cell" xfId="20" builtinId="24"/>
+    <cellStyle name="Total" xfId="21" builtinId="25"/>
+    <cellStyle name="Good" xfId="22" builtinId="26"/>
+    <cellStyle name="Bad" xfId="23" builtinId="27"/>
+    <cellStyle name="Neutral" xfId="24" builtinId="28"/>
+    <cellStyle name="Accent1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - Accent1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - Accent1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - Accent1" xfId="28" builtinId="32"/>
+    <cellStyle name="Accent2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - Accent2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - Accent2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - Accent2" xfId="32" builtinId="36"/>
+    <cellStyle name="Accent3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - Accent3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - Accent3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - Accent3" xfId="36" builtinId="40"/>
+    <cellStyle name="Accent4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - Accent4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - Accent4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - Accent4" xfId="40" builtinId="44"/>
+    <cellStyle name="Accent5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - Accent5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - Accent5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - Accent5" xfId="44" builtinId="48"/>
+    <cellStyle name="Accent6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - Accent6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - Accent6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3023,31 +2477,52 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:CB66"/>
+  <dimension ref="A1:AE66"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
-    <col min="4" max="4" width="4.625" customWidth="1"/>
-    <col min="5" max="5" width="13.375" customWidth="1"/>
-    <col min="8" max="11" width="4" customWidth="1"/>
-    <col min="12" max="12" width="19.875" customWidth="1"/>
+    <col min="1" max="1" width="8.375" customWidth="1"/>
+    <col min="2" max="2" width="9.375" customWidth="1"/>
+    <col min="3" max="3" width="7.375" customWidth="1"/>
+    <col min="4" max="4" width="9.375" customWidth="1"/>
+    <col min="5" max="5" width="6.625" customWidth="1"/>
+    <col min="6" max="6" width="14.375" customWidth="1"/>
+    <col min="7" max="7" width="10.125" customWidth="1"/>
+    <col min="8" max="8" width="10.75" customWidth="1"/>
+    <col min="9" max="9" width="19.75" customWidth="1"/>
+    <col min="10" max="10" width="10" customWidth="1"/>
+    <col min="11" max="11" width="11.375" customWidth="1"/>
+    <col min="12" max="12" width="22.5" customWidth="1"/>
+    <col min="13" max="13" width="31.875" customWidth="1"/>
+    <col min="14" max="14" width="12.625" customWidth="1"/>
     <col min="15" max="15" width="17" customWidth="1"/>
-    <col min="16" max="16" width="7.5" customWidth="1"/>
-    <col min="17" max="70" width="2.25" hidden="1" customWidth="1" outlineLevel="1"/>
-    <col min="71" max="71" width="9" collapsed="1"/>
-    <col min="72" max="72" width="9" customWidth="1"/>
-    <col min="76" max="76" width="14.875" customWidth="1"/>
-    <col min="77" max="77" width="13.5" customWidth="1"/>
-    <col min="78" max="78" width="14.875" customWidth="1"/>
-    <col min="79" max="79" width="20.375" customWidth="1"/>
-    <col min="80" max="80" width="14.875" customWidth="1"/>
-    <col min="81" max="81" width="13.75" customWidth="1"/>
-    <col min="82" max="82" width="14.875" customWidth="1"/>
-    <col min="83" max="83" width="13.75" customWidth="1"/>
-    <col min="84" max="84" width="14.875" customWidth="1"/>
-    <col min="85" max="85" width="13.75" customWidth="1"/>
+    <col min="16" max="16" width="12.625" customWidth="1"/>
+    <col min="17" max="17" width="11.5" customWidth="1"/>
+    <col min="18" max="18" width="12.625" customWidth="1"/>
+    <col min="19" max="19" width="11.5" customWidth="1"/>
+    <col min="20" max="20" width="12.625" customWidth="1"/>
+    <col min="21" max="21" width="11.5" customWidth="1"/>
+    <col min="22" max="22" width="12.625" customWidth="1"/>
+    <col min="23" max="23" width="11.5" customWidth="1"/>
+    <col min="24" max="24" width="12.625" customWidth="1"/>
+    <col min="25" max="25" width="11.5" customWidth="1"/>
+    <col min="26" max="26" width="12.625" customWidth="1"/>
+    <col min="27" max="27" width="11.5" customWidth="1"/>
+    <col min="28" max="28" width="12.625" customWidth="1"/>
+    <col min="29" max="29" width="11.5" customWidth="1"/>
+    <col min="30" max="30" width="13.75" customWidth="1"/>
+    <col min="31" max="31" width="12.625" customWidth="1"/>
+    <col min="32" max="32" width="13.5" customWidth="1"/>
+    <col min="33" max="33" width="14.875" customWidth="1"/>
+    <col min="34" max="34" width="20.375" customWidth="1"/>
+    <col min="35" max="35" width="14.875" customWidth="1"/>
+    <col min="36" max="36" width="13.75" customWidth="1"/>
+    <col min="37" max="37" width="14.875" customWidth="1"/>
+    <col min="38" max="38" width="13.75" customWidth="1"/>
+    <col min="39" max="39" width="14.875" customWidth="1"/>
+    <col min="40" max="40" width="13.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:80">
+    <row r="1" spans="1:31">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3141,2015 +2616,1739 @@
       <c r="AE1" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
-        <v>31</v>
-      </c>
-      <c r="AG1" t="s">
-        <v>32</v>
-      </c>
-      <c r="AH1" t="s">
-        <v>33</v>
-      </c>
-      <c r="AI1" t="s">
-        <v>34</v>
-      </c>
-      <c r="AJ1" t="s">
-        <v>35</v>
-      </c>
-      <c r="AK1" t="s">
-        <v>36</v>
-      </c>
-      <c r="AL1" t="s">
-        <v>37</v>
-      </c>
-      <c r="AM1" t="s">
-        <v>38</v>
-      </c>
-      <c r="AN1" t="s">
-        <v>39</v>
-      </c>
-      <c r="AO1" t="s">
-        <v>40</v>
-      </c>
-      <c r="AP1" t="s">
-        <v>41</v>
-      </c>
-      <c r="AQ1" t="s">
-        <v>42</v>
-      </c>
-      <c r="AR1" t="s">
-        <v>43</v>
-      </c>
-      <c r="AS1" t="s">
-        <v>44</v>
-      </c>
-      <c r="AT1" t="s">
-        <v>45</v>
-      </c>
-      <c r="AU1" t="s">
-        <v>46</v>
-      </c>
-      <c r="AV1" t="s">
-        <v>47</v>
-      </c>
-      <c r="AW1" t="s">
-        <v>48</v>
-      </c>
-      <c r="AX1" t="s">
-        <v>49</v>
-      </c>
-      <c r="AY1" t="s">
-        <v>50</v>
-      </c>
-      <c r="AZ1" t="s">
-        <v>51</v>
-      </c>
-      <c r="BA1" t="s">
-        <v>52</v>
-      </c>
-      <c r="BB1" t="s">
-        <v>53</v>
-      </c>
-      <c r="BC1" t="s">
-        <v>54</v>
-      </c>
-      <c r="BD1" t="s">
-        <v>55</v>
-      </c>
-      <c r="BE1" t="s">
-        <v>56</v>
-      </c>
-      <c r="BF1" t="s">
-        <v>57</v>
-      </c>
-      <c r="BG1" t="s">
-        <v>58</v>
-      </c>
-      <c r="BH1" t="s">
-        <v>59</v>
-      </c>
-      <c r="BI1" t="s">
-        <v>60</v>
-      </c>
-      <c r="BJ1" t="s">
-        <v>61</v>
-      </c>
-      <c r="BK1" t="s">
-        <v>62</v>
-      </c>
-      <c r="BL1" t="s">
-        <v>63</v>
-      </c>
-      <c r="BM1" t="s">
-        <v>64</v>
-      </c>
-      <c r="BN1" t="s">
-        <v>65</v>
-      </c>
-      <c r="BO1" t="s">
-        <v>66</v>
-      </c>
-      <c r="BP1" t="s">
-        <v>67</v>
-      </c>
-      <c r="BQ1" t="s">
-        <v>68</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>69</v>
-      </c>
-      <c r="BS1" t="s">
-        <v>70</v>
-      </c>
-      <c r="BT1" t="s">
-        <v>71</v>
-      </c>
-      <c r="BU1" t="s">
-        <v>72</v>
-      </c>
-      <c r="BV1" t="s">
-        <v>73</v>
-      </c>
-      <c r="BW1" t="s">
-        <v>74</v>
-      </c>
-      <c r="BX1" t="s">
-        <v>75</v>
-      </c>
-      <c r="BY1" t="s">
-        <v>76</v>
-      </c>
-      <c r="BZ1" t="s">
-        <v>77</v>
-      </c>
-      <c r="CA1" t="s">
-        <v>78</v>
-      </c>
-      <c r="CB1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="2" spans="1:80">
+    </row>
+    <row r="2" spans="1:31">
       <c r="A2">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
-        <v>80</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2" t="s">
-        <v>81</v>
+      <c r="D2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
       </c>
       <c r="F2" t="s">
-        <v>82</v>
+        <v>32</v>
       </c>
       <c r="G2" t="s">
-        <v>83</v>
+        <v>33</v>
       </c>
       <c r="H2" t="s">
-        <v>81</v>
+        <v>34</v>
+      </c>
+      <c r="I2" t="s">
+        <v>32</v>
       </c>
       <c r="L2" t="s">
-        <v>84</v>
+        <v>35</v>
       </c>
       <c r="M2" t="s">
-        <v>85</v>
-      </c>
-      <c r="BS2" t="s">
-        <v>86</v>
-      </c>
-      <c r="BT2" t="s">
-        <v>87</v>
-      </c>
-      <c r="BU2" t="s">
-        <v>88</v>
-      </c>
-      <c r="BV2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="3" spans="1:80">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3" t="s">
-        <v>91</v>
+      <c r="D3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
       </c>
       <c r="F3" t="s">
-        <v>92</v>
-      </c>
-      <c r="H3" t="s">
-        <v>93</v>
+        <v>38</v>
+      </c>
+      <c r="G3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I3" t="s">
+        <v>40</v>
       </c>
       <c r="L3" t="s">
-        <v>94</v>
+        <v>41</v>
       </c>
       <c r="M3" t="s">
-        <v>95</v>
-      </c>
-      <c r="BS3" t="s">
-        <v>96</v>
-      </c>
-      <c r="BT3" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="BU3" t="s">
-        <v>88</v>
-      </c>
-      <c r="BV3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="4" spans="1:80">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31">
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="C4" t="s">
-        <v>99</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4" t="s">
-        <v>100</v>
+      <c r="D4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
       </c>
       <c r="F4" t="s">
-        <v>101</v>
-      </c>
-      <c r="H4" t="s">
-        <v>93</v>
+        <v>44</v>
+      </c>
+      <c r="G4" t="s">
+        <v>45</v>
+      </c>
+      <c r="I4" t="s">
+        <v>40</v>
       </c>
       <c r="L4" t="s">
-        <v>102</v>
+        <v>46</v>
       </c>
       <c r="M4" t="s">
-        <v>103</v>
-      </c>
-      <c r="BS4" t="s">
-        <v>96</v>
-      </c>
-      <c r="BT4" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="BU4" t="s">
-        <v>88</v>
-      </c>
-      <c r="BV4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" spans="1:80">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31">
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="C5" t="s">
-        <v>105</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5" t="s">
-        <v>106</v>
+      <c r="D5" t="s">
+        <v>48</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>107</v>
-      </c>
-      <c r="H5" t="s">
-        <v>93</v>
+        <v>49</v>
+      </c>
+      <c r="G5" t="s">
+        <v>50</v>
+      </c>
+      <c r="I5" t="s">
+        <v>40</v>
       </c>
       <c r="L5" t="s">
-        <v>108</v>
+        <v>51</v>
       </c>
       <c r="M5" t="s">
-        <v>109</v>
-      </c>
-      <c r="BS5" t="s">
-        <v>96</v>
-      </c>
-      <c r="BT5" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="BU5" t="s">
-        <v>88</v>
-      </c>
-      <c r="BV5" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="6" spans="1:80">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31">
       <c r="A6">
         <v>4</v>
       </c>
-      <c r="C6" t="s">
-        <v>111</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6" t="s">
-        <v>112</v>
+      <c r="D6" t="s">
+        <v>53</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>113</v>
-      </c>
-      <c r="H6" t="s">
-        <v>93</v>
+        <v>54</v>
+      </c>
+      <c r="G6" t="s">
+        <v>55</v>
+      </c>
+      <c r="I6" t="s">
+        <v>40</v>
       </c>
       <c r="L6" t="s">
-        <v>114</v>
+        <v>56</v>
       </c>
       <c r="M6" t="s">
-        <v>115</v>
-      </c>
-      <c r="BS6" t="s">
-        <v>96</v>
-      </c>
-      <c r="BT6" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="BU6" t="s">
-        <v>88</v>
-      </c>
-      <c r="BV6" s="1" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="7" spans="1:80">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31">
       <c r="A7">
         <v>5</v>
       </c>
-      <c r="C7" t="s">
-        <v>117</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7" t="s">
-        <v>118</v>
+      <c r="D7" t="s">
+        <v>58</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>119</v>
-      </c>
-      <c r="H7" t="s">
-        <v>93</v>
+        <v>59</v>
+      </c>
+      <c r="G7" t="s">
+        <v>60</v>
+      </c>
+      <c r="I7" t="s">
+        <v>40</v>
       </c>
       <c r="L7" t="s">
-        <v>120</v>
+        <v>61</v>
       </c>
       <c r="M7" t="s">
-        <v>121</v>
-      </c>
-      <c r="BS7" t="s">
-        <v>96</v>
-      </c>
-      <c r="BT7" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="BU7" t="s">
-        <v>88</v>
-      </c>
-      <c r="BV7" s="1" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="8" spans="1:80">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31">
       <c r="A8">
         <v>6</v>
       </c>
-      <c r="C8" t="s">
-        <v>123</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8" t="s">
-        <v>124</v>
+      <c r="D8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>125</v>
-      </c>
-      <c r="H8" t="s">
-        <v>93</v>
+        <v>64</v>
+      </c>
+      <c r="G8" t="s">
+        <v>65</v>
+      </c>
+      <c r="I8" t="s">
+        <v>40</v>
       </c>
       <c r="L8" t="s">
-        <v>126</v>
+        <v>66</v>
       </c>
       <c r="M8" t="s">
-        <v>127</v>
-      </c>
-      <c r="BS8" t="s">
-        <v>96</v>
-      </c>
-      <c r="BT8" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="BU8" t="s">
-        <v>88</v>
-      </c>
-      <c r="BV8" s="1" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="9" spans="1:80">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31">
       <c r="A9">
         <v>7</v>
       </c>
-      <c r="C9" t="s">
-        <v>129</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9" t="s">
-        <v>129</v>
+      <c r="D9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>130</v>
-      </c>
-      <c r="H9" t="s">
-        <v>93</v>
+        <v>68</v>
+      </c>
+      <c r="G9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I9" t="s">
+        <v>40</v>
       </c>
       <c r="L9" t="s">
-        <v>131</v>
+        <v>70</v>
       </c>
       <c r="M9" t="s">
-        <v>132</v>
-      </c>
-      <c r="BS9" t="s">
-        <v>96</v>
-      </c>
-      <c r="BT9" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="BU9" t="s">
-        <v>88</v>
-      </c>
-      <c r="BV9" s="1" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="10" spans="1:80">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31">
       <c r="A10">
         <v>8</v>
       </c>
-      <c r="C10" t="s">
-        <v>134</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10" t="s">
-        <v>135</v>
+      <c r="D10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E10">
+        <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>136</v>
-      </c>
-      <c r="H10" t="s">
-        <v>93</v>
+        <v>73</v>
+      </c>
+      <c r="G10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I10" t="s">
+        <v>40</v>
       </c>
       <c r="L10" t="s">
-        <v>137</v>
+        <v>75</v>
       </c>
       <c r="M10" t="s">
-        <v>138</v>
-      </c>
-      <c r="BS10" t="s">
-        <v>96</v>
-      </c>
-      <c r="BT10" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="BU10" t="s">
-        <v>88</v>
-      </c>
-      <c r="BV10" s="1" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="11" spans="1:80">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31">
       <c r="A11">
         <v>11</v>
       </c>
-      <c r="C11" t="s">
+      <c r="D11" t="s">
+        <v>31</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" t="s">
+        <v>78</v>
+      </c>
+      <c r="I11" t="s">
+        <v>79</v>
+      </c>
+      <c r="L11" t="s">
         <v>80</v>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11" t="s">
-        <v>140</v>
-      </c>
-      <c r="F11" t="s">
-        <v>141</v>
-      </c>
-      <c r="H11" t="s">
-        <v>142</v>
-      </c>
-      <c r="L11" t="s">
-        <v>143</v>
-      </c>
       <c r="M11" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="12" spans="1:80">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31">
       <c r="A12">
         <v>12</v>
       </c>
-      <c r="C12" t="s">
-        <v>80</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12" t="s">
-        <v>145</v>
+      <c r="D12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12">
+        <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>146</v>
-      </c>
-      <c r="H12" t="s">
-        <v>147</v>
+        <v>82</v>
+      </c>
+      <c r="G12" t="s">
+        <v>83</v>
+      </c>
+      <c r="I12" t="s">
+        <v>84</v>
       </c>
       <c r="L12" t="s">
-        <v>148</v>
+        <v>85</v>
       </c>
       <c r="M12" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="13" spans="1:80">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31">
       <c r="A13">
         <v>13</v>
       </c>
-      <c r="C13" t="s">
-        <v>80</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13" t="s">
-        <v>150</v>
+      <c r="D13" t="s">
+        <v>31</v>
+      </c>
+      <c r="E13">
+        <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>151</v>
-      </c>
-      <c r="H13" t="s">
-        <v>152</v>
+        <v>87</v>
+      </c>
+      <c r="G13" t="s">
+        <v>88</v>
+      </c>
+      <c r="I13" t="s">
+        <v>89</v>
       </c>
       <c r="L13" t="s">
-        <v>153</v>
+        <v>90</v>
       </c>
       <c r="M13" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="14" spans="1:80">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31">
       <c r="A14">
         <v>14</v>
       </c>
-      <c r="C14" t="s">
-        <v>80</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14" t="s">
-        <v>155</v>
+      <c r="D14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
       </c>
       <c r="F14" t="s">
-        <v>156</v>
-      </c>
-      <c r="H14" t="s">
-        <v>157</v>
+        <v>92</v>
+      </c>
+      <c r="G14" t="s">
+        <v>93</v>
+      </c>
+      <c r="I14" t="s">
+        <v>94</v>
       </c>
       <c r="L14" t="s">
-        <v>158</v>
+        <v>95</v>
       </c>
       <c r="M14" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="15" spans="1:80">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31">
       <c r="A15">
         <v>15</v>
       </c>
-      <c r="C15" t="s">
-        <v>80</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15" t="s">
-        <v>160</v>
+      <c r="D15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E15">
+        <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>161</v>
+        <v>97</v>
       </c>
       <c r="G15" t="s">
-        <v>162</v>
+        <v>98</v>
       </c>
       <c r="H15" t="s">
-        <v>163</v>
+        <v>99</v>
+      </c>
+      <c r="I15" t="s">
+        <v>100</v>
       </c>
       <c r="L15" t="s">
-        <v>164</v>
+        <v>101</v>
       </c>
       <c r="M15" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="16" spans="1:80">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31">
       <c r="A16">
         <v>21</v>
       </c>
-      <c r="C16" t="s">
-        <v>80</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16" t="s">
-        <v>166</v>
+      <c r="D16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>167</v>
-      </c>
-      <c r="H16" t="s">
-        <v>168</v>
+        <v>103</v>
+      </c>
+      <c r="G16" t="s">
+        <v>104</v>
+      </c>
+      <c r="I16" t="s">
+        <v>105</v>
       </c>
       <c r="L16" t="s">
-        <v>169</v>
+        <v>106</v>
       </c>
       <c r="M16" t="s">
-        <v>170</v>
+        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17">
         <v>22</v>
       </c>
-      <c r="C17" t="s">
-        <v>80</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17" t="s">
-        <v>171</v>
+      <c r="D17" t="s">
+        <v>31</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>172</v>
-      </c>
-      <c r="H17" t="s">
-        <v>173</v>
+        <v>108</v>
+      </c>
+      <c r="G17" t="s">
+        <v>109</v>
+      </c>
+      <c r="I17" t="s">
+        <v>110</v>
       </c>
       <c r="L17" t="s">
-        <v>174</v>
+        <v>111</v>
       </c>
       <c r="M17" t="s">
-        <v>175</v>
+        <v>112</v>
       </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18">
         <v>23</v>
       </c>
-      <c r="C18" t="s">
-        <v>80</v>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18" t="s">
-        <v>176</v>
+      <c r="D18" t="s">
+        <v>31</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>177</v>
-      </c>
-      <c r="H18" t="s">
-        <v>178</v>
+        <v>113</v>
+      </c>
+      <c r="G18" t="s">
+        <v>114</v>
+      </c>
+      <c r="I18" t="s">
+        <v>115</v>
       </c>
       <c r="L18" t="s">
-        <v>179</v>
+        <v>116</v>
       </c>
       <c r="M18" t="s">
-        <v>180</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19">
         <v>31</v>
       </c>
-      <c r="C19" t="s">
-        <v>80</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19" t="s">
-        <v>181</v>
+      <c r="D19" t="s">
+        <v>31</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>182</v>
-      </c>
-      <c r="H19" t="s">
-        <v>183</v>
+        <v>118</v>
+      </c>
+      <c r="G19" t="s">
+        <v>119</v>
+      </c>
+      <c r="I19" t="s">
+        <v>120</v>
       </c>
       <c r="L19" t="s">
-        <v>184</v>
+        <v>121</v>
       </c>
       <c r="M19" t="s">
-        <v>185</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20">
         <v>32</v>
       </c>
-      <c r="C20" t="s">
-        <v>80</v>
-      </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20" t="s">
-        <v>186</v>
+      <c r="D20" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>187</v>
-      </c>
-      <c r="H20" t="s">
-        <v>188</v>
+        <v>123</v>
+      </c>
+      <c r="G20" t="s">
+        <v>124</v>
+      </c>
+      <c r="I20" t="s">
+        <v>125</v>
       </c>
       <c r="L20" t="s">
-        <v>189</v>
+        <v>126</v>
       </c>
       <c r="M20" t="s">
-        <v>190</v>
+        <v>127</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21">
         <v>33</v>
       </c>
-      <c r="C21" t="s">
-        <v>80</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21" t="s">
-        <v>191</v>
+      <c r="D21" t="s">
+        <v>31</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>192</v>
-      </c>
-      <c r="H21" t="s">
-        <v>193</v>
+        <v>128</v>
+      </c>
+      <c r="G21" t="s">
+        <v>129</v>
+      </c>
+      <c r="I21" t="s">
+        <v>130</v>
       </c>
       <c r="L21" t="s">
-        <v>194</v>
+        <v>131</v>
       </c>
       <c r="M21" t="s">
-        <v>195</v>
+        <v>132</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22">
         <v>34</v>
       </c>
-      <c r="C22" t="s">
-        <v>80</v>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22" t="s">
-        <v>196</v>
+      <c r="D22" t="s">
+        <v>31</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>197</v>
-      </c>
-      <c r="H22" t="s">
-        <v>198</v>
+        <v>133</v>
+      </c>
+      <c r="G22" t="s">
+        <v>134</v>
+      </c>
+      <c r="I22" t="s">
+        <v>135</v>
       </c>
       <c r="L22" t="s">
-        <v>199</v>
+        <v>136</v>
       </c>
       <c r="M22" t="s">
-        <v>200</v>
+        <v>137</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23">
         <v>35</v>
       </c>
-      <c r="C23" t="s">
-        <v>80</v>
-      </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="E23" t="s">
-        <v>201</v>
+      <c r="D23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23">
+        <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>202</v>
-      </c>
-      <c r="H23" t="s">
-        <v>203</v>
+        <v>138</v>
+      </c>
+      <c r="G23" t="s">
+        <v>139</v>
+      </c>
+      <c r="I23" t="s">
+        <v>140</v>
       </c>
       <c r="L23" t="s">
-        <v>204</v>
+        <v>141</v>
       </c>
       <c r="M23" t="s">
-        <v>205</v>
+        <v>142</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24">
         <v>36</v>
       </c>
-      <c r="C24" t="s">
-        <v>80</v>
-      </c>
-      <c r="D24">
-        <v>1</v>
-      </c>
-      <c r="E24" t="s">
-        <v>206</v>
+      <c r="D24" t="s">
+        <v>31</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>207</v>
-      </c>
-      <c r="H24" t="s">
-        <v>208</v>
+        <v>143</v>
+      </c>
+      <c r="G24" t="s">
+        <v>144</v>
+      </c>
+      <c r="I24" t="s">
+        <v>145</v>
       </c>
       <c r="L24" t="s">
-        <v>209</v>
+        <v>146</v>
       </c>
       <c r="M24" t="s">
-        <v>210</v>
+        <v>147</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25">
         <v>37</v>
       </c>
-      <c r="C25" t="s">
-        <v>80</v>
-      </c>
-      <c r="D25">
-        <v>1</v>
-      </c>
-      <c r="E25" t="s">
-        <v>211</v>
+      <c r="D25" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>212</v>
-      </c>
-      <c r="H25" t="s">
-        <v>213</v>
+        <v>148</v>
+      </c>
+      <c r="G25" t="s">
+        <v>149</v>
+      </c>
+      <c r="I25" t="s">
+        <v>150</v>
       </c>
       <c r="L25" t="s">
-        <v>214</v>
+        <v>151</v>
       </c>
       <c r="M25" t="s">
-        <v>215</v>
+        <v>152</v>
       </c>
     </row>
     <row r="26" spans="1:13">
       <c r="A26">
         <v>41</v>
       </c>
-      <c r="C26" t="s">
-        <v>80</v>
-      </c>
-      <c r="D26">
-        <v>1</v>
-      </c>
-      <c r="E26" t="s">
-        <v>216</v>
+      <c r="D26" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>217</v>
+        <v>153</v>
       </c>
       <c r="G26" t="s">
-        <v>218</v>
+        <v>154</v>
       </c>
       <c r="H26" t="s">
-        <v>219</v>
+        <v>155</v>
+      </c>
+      <c r="I26" t="s">
+        <v>156</v>
       </c>
       <c r="L26" t="s">
-        <v>220</v>
+        <v>157</v>
       </c>
       <c r="M26" t="s">
-        <v>221</v>
+        <v>158</v>
       </c>
     </row>
     <row r="27" spans="1:13">
       <c r="A27">
         <v>42</v>
       </c>
-      <c r="C27" t="s">
-        <v>80</v>
-      </c>
-      <c r="D27">
-        <v>1</v>
-      </c>
-      <c r="E27" t="s">
-        <v>222</v>
+      <c r="D27" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>223</v>
+        <v>159</v>
       </c>
       <c r="G27" t="s">
-        <v>224</v>
+        <v>160</v>
       </c>
       <c r="H27" t="s">
-        <v>225</v>
+        <v>161</v>
+      </c>
+      <c r="I27" t="s">
+        <v>162</v>
       </c>
       <c r="L27" t="s">
-        <v>226</v>
+        <v>163</v>
       </c>
       <c r="M27" t="s">
-        <v>227</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28">
         <v>43</v>
       </c>
-      <c r="C28" t="s">
-        <v>80</v>
-      </c>
-      <c r="D28">
-        <v>1</v>
-      </c>
-      <c r="E28" t="s">
-        <v>228</v>
+      <c r="D28" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>229</v>
-      </c>
-      <c r="H28" t="s">
-        <v>230</v>
+        <v>165</v>
+      </c>
+      <c r="G28" t="s">
+        <v>166</v>
+      </c>
+      <c r="I28" t="s">
+        <v>167</v>
       </c>
       <c r="L28" t="s">
-        <v>231</v>
+        <v>168</v>
       </c>
       <c r="M28" t="s">
-        <v>232</v>
+        <v>169</v>
       </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29">
         <v>44</v>
       </c>
-      <c r="C29" t="s">
-        <v>80</v>
-      </c>
-      <c r="D29">
-        <v>1</v>
-      </c>
-      <c r="E29" t="s">
-        <v>233</v>
+      <c r="D29" t="s">
+        <v>31</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>234</v>
-      </c>
-      <c r="H29" t="s">
-        <v>235</v>
+        <v>170</v>
+      </c>
+      <c r="G29" t="s">
+        <v>171</v>
+      </c>
+      <c r="I29" t="s">
+        <v>172</v>
       </c>
       <c r="L29" t="s">
-        <v>236</v>
+        <v>173</v>
       </c>
       <c r="M29" t="s">
-        <v>237</v>
+        <v>174</v>
       </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30">
         <v>45</v>
       </c>
-      <c r="C30" t="s">
-        <v>80</v>
-      </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
-      <c r="E30" t="s">
-        <v>238</v>
+      <c r="D30" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>239</v>
-      </c>
-      <c r="H30" t="s">
-        <v>240</v>
+        <v>175</v>
+      </c>
+      <c r="G30" t="s">
+        <v>176</v>
+      </c>
+      <c r="I30" t="s">
+        <v>177</v>
       </c>
       <c r="L30" t="s">
-        <v>241</v>
+        <v>178</v>
       </c>
       <c r="M30" t="s">
-        <v>242</v>
+        <v>179</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31">
         <v>46</v>
       </c>
-      <c r="C31" t="s">
-        <v>80</v>
-      </c>
-      <c r="D31">
-        <v>1</v>
-      </c>
-      <c r="E31" t="s">
-        <v>243</v>
+      <c r="D31" t="s">
+        <v>31</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>244</v>
-      </c>
-      <c r="H31" t="s">
-        <v>245</v>
+        <v>180</v>
+      </c>
+      <c r="G31" t="s">
+        <v>181</v>
+      </c>
+      <c r="I31" t="s">
+        <v>182</v>
       </c>
       <c r="L31" t="s">
-        <v>246</v>
+        <v>183</v>
       </c>
       <c r="M31" t="s">
-        <v>247</v>
+        <v>184</v>
       </c>
     </row>
     <row r="32" spans="1:13">
       <c r="A32">
         <v>50</v>
       </c>
-      <c r="C32" t="s">
-        <v>80</v>
-      </c>
-      <c r="D32">
-        <v>1</v>
-      </c>
-      <c r="E32" t="s">
-        <v>248</v>
+      <c r="D32" t="s">
+        <v>31</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>249</v>
-      </c>
-      <c r="H32" t="s">
-        <v>250</v>
+        <v>185</v>
+      </c>
+      <c r="G32" t="s">
+        <v>186</v>
+      </c>
+      <c r="I32" t="s">
+        <v>187</v>
       </c>
       <c r="L32" t="s">
-        <v>251</v>
+        <v>188</v>
       </c>
       <c r="M32" t="s">
-        <v>252</v>
+        <v>189</v>
       </c>
     </row>
     <row r="33" spans="1:13">
       <c r="A33">
         <v>51</v>
       </c>
-      <c r="C33" t="s">
-        <v>80</v>
-      </c>
-      <c r="D33">
-        <v>1</v>
-      </c>
-      <c r="E33" t="s">
-        <v>253</v>
+      <c r="D33" t="s">
+        <v>31</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>254</v>
-      </c>
-      <c r="H33" t="s">
-        <v>255</v>
+        <v>190</v>
+      </c>
+      <c r="G33" t="s">
+        <v>191</v>
+      </c>
+      <c r="I33" t="s">
+        <v>192</v>
       </c>
       <c r="L33" t="s">
-        <v>256</v>
+        <v>193</v>
       </c>
       <c r="M33" t="s">
-        <v>257</v>
+        <v>194</v>
       </c>
     </row>
     <row r="34" spans="1:13">
       <c r="A34">
         <v>52</v>
       </c>
-      <c r="C34" t="s">
-        <v>80</v>
-      </c>
-      <c r="D34">
-        <v>1</v>
-      </c>
-      <c r="E34" t="s">
-        <v>258</v>
+      <c r="D34" t="s">
+        <v>31</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>259</v>
-      </c>
-      <c r="H34" t="s">
-        <v>260</v>
+        <v>195</v>
+      </c>
+      <c r="G34" t="s">
+        <v>196</v>
+      </c>
+      <c r="I34" t="s">
+        <v>197</v>
       </c>
       <c r="L34" t="s">
-        <v>261</v>
+        <v>198</v>
       </c>
       <c r="M34" t="s">
-        <v>262</v>
+        <v>199</v>
       </c>
     </row>
     <row r="35" spans="1:13">
       <c r="A35">
         <v>53</v>
       </c>
-      <c r="C35" t="s">
-        <v>80</v>
-      </c>
-      <c r="D35">
-        <v>1</v>
-      </c>
-      <c r="E35" t="s">
-        <v>263</v>
+      <c r="D35" t="s">
+        <v>31</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>264</v>
-      </c>
-      <c r="H35" t="s">
-        <v>265</v>
+        <v>200</v>
+      </c>
+      <c r="G35" t="s">
+        <v>201</v>
+      </c>
+      <c r="I35" t="s">
+        <v>202</v>
       </c>
       <c r="L35" t="s">
-        <v>266</v>
+        <v>203</v>
       </c>
       <c r="M35" t="s">
-        <v>267</v>
+        <v>204</v>
       </c>
     </row>
     <row r="36" spans="1:13">
       <c r="A36">
         <v>54</v>
       </c>
-      <c r="C36" t="s">
-        <v>80</v>
-      </c>
-      <c r="D36">
-        <v>1</v>
-      </c>
-      <c r="E36" t="s">
-        <v>268</v>
+      <c r="D36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>269</v>
-      </c>
-      <c r="H36" t="s">
-        <v>270</v>
+        <v>205</v>
+      </c>
+      <c r="G36" t="s">
+        <v>206</v>
+      </c>
+      <c r="I36" t="s">
+        <v>207</v>
       </c>
       <c r="L36" t="s">
-        <v>271</v>
+        <v>208</v>
       </c>
       <c r="M36" t="s">
-        <v>272</v>
+        <v>209</v>
       </c>
     </row>
     <row r="37" spans="1:13">
       <c r="A37">
         <v>61</v>
       </c>
-      <c r="C37" t="s">
-        <v>80</v>
-      </c>
-      <c r="D37">
-        <v>1</v>
-      </c>
-      <c r="E37" t="s">
-        <v>273</v>
+      <c r="D37" t="s">
+        <v>31</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>274</v>
-      </c>
-      <c r="H37" t="s">
-        <v>275</v>
+        <v>210</v>
+      </c>
+      <c r="G37" t="s">
+        <v>211</v>
+      </c>
+      <c r="I37" t="s">
+        <v>212</v>
       </c>
       <c r="L37" t="s">
-        <v>276</v>
+        <v>213</v>
       </c>
       <c r="M37" t="s">
-        <v>277</v>
+        <v>214</v>
       </c>
     </row>
     <row r="38" spans="1:13">
       <c r="A38">
         <v>62</v>
       </c>
-      <c r="C38" t="s">
-        <v>80</v>
-      </c>
-      <c r="D38">
-        <v>1</v>
-      </c>
-      <c r="E38" t="s">
-        <v>278</v>
+      <c r="D38" t="s">
+        <v>31</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>279</v>
-      </c>
-      <c r="H38" t="s">
-        <v>280</v>
+        <v>215</v>
+      </c>
+      <c r="G38" t="s">
+        <v>216</v>
+      </c>
+      <c r="I38" t="s">
+        <v>217</v>
       </c>
       <c r="L38" t="s">
-        <v>281</v>
+        <v>218</v>
       </c>
       <c r="M38" t="s">
-        <v>282</v>
+        <v>219</v>
       </c>
     </row>
     <row r="39" spans="1:13">
       <c r="A39">
         <v>63</v>
       </c>
-      <c r="C39" t="s">
-        <v>80</v>
-      </c>
-      <c r="D39">
-        <v>1</v>
-      </c>
-      <c r="E39" t="s">
-        <v>283</v>
+      <c r="D39" t="s">
+        <v>31</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>284</v>
-      </c>
-      <c r="H39" t="s">
-        <v>285</v>
+        <v>220</v>
+      </c>
+      <c r="G39" t="s">
+        <v>221</v>
+      </c>
+      <c r="I39" t="s">
+        <v>222</v>
       </c>
       <c r="L39" t="s">
-        <v>286</v>
+        <v>223</v>
       </c>
       <c r="M39" t="s">
-        <v>287</v>
+        <v>224</v>
       </c>
     </row>
     <row r="40" spans="1:13">
       <c r="A40">
         <v>64</v>
       </c>
-      <c r="C40" t="s">
-        <v>80</v>
-      </c>
-      <c r="D40">
-        <v>1</v>
-      </c>
-      <c r="E40" t="s">
-        <v>288</v>
+      <c r="D40" t="s">
+        <v>31</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>289</v>
-      </c>
-      <c r="H40" t="s">
-        <v>290</v>
+        <v>225</v>
+      </c>
+      <c r="G40" t="s">
+        <v>226</v>
+      </c>
+      <c r="I40" t="s">
+        <v>227</v>
       </c>
       <c r="L40" t="s">
-        <v>291</v>
+        <v>228</v>
       </c>
       <c r="M40" t="s">
-        <v>292</v>
+        <v>229</v>
       </c>
     </row>
     <row r="41" spans="1:13">
       <c r="A41">
         <v>65</v>
       </c>
-      <c r="C41" t="s">
-        <v>80</v>
-      </c>
-      <c r="D41">
-        <v>1</v>
-      </c>
-      <c r="E41" t="s">
-        <v>293</v>
+      <c r="D41" t="s">
+        <v>31</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
       </c>
       <c r="F41" t="s">
-        <v>294</v>
-      </c>
-      <c r="H41" t="s">
-        <v>295</v>
+        <v>230</v>
+      </c>
+      <c r="G41" t="s">
+        <v>231</v>
+      </c>
+      <c r="I41" t="s">
+        <v>232</v>
       </c>
       <c r="L41" t="s">
-        <v>296</v>
+        <v>233</v>
       </c>
       <c r="M41" t="s">
-        <v>297</v>
+        <v>234</v>
       </c>
     </row>
     <row r="42" spans="1:13">
       <c r="A42">
         <v>9000</v>
       </c>
-      <c r="C42" t="s">
-        <v>80</v>
-      </c>
-      <c r="D42">
-        <v>1</v>
-      </c>
-      <c r="E42" t="s">
-        <v>298</v>
+      <c r="D42" t="s">
+        <v>31</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>299</v>
+        <v>235</v>
       </c>
       <c r="G42" t="s">
-        <v>300</v>
+        <v>236</v>
       </c>
       <c r="H42" t="s">
-        <v>301</v>
+        <v>237</v>
+      </c>
+      <c r="I42" t="s">
+        <v>238</v>
       </c>
       <c r="L42" t="s">
-        <v>302</v>
+        <v>239</v>
       </c>
       <c r="M42" t="s">
-        <v>303</v>
+        <v>240</v>
       </c>
     </row>
     <row r="43" spans="1:13">
       <c r="A43">
         <v>9001</v>
       </c>
-      <c r="C43" t="s">
-        <v>80</v>
-      </c>
-      <c r="D43">
-        <v>1</v>
-      </c>
-      <c r="E43" t="s">
-        <v>304</v>
+      <c r="D43" t="s">
+        <v>31</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>305</v>
-      </c>
-      <c r="H43" t="s">
-        <v>306</v>
+        <v>241</v>
+      </c>
+      <c r="G43" t="s">
+        <v>242</v>
+      </c>
+      <c r="I43" t="s">
+        <v>243</v>
       </c>
       <c r="L43" t="s">
-        <v>307</v>
+        <v>244</v>
       </c>
       <c r="M43" t="s">
-        <v>308</v>
+        <v>245</v>
       </c>
     </row>
     <row r="44" spans="1:13">
       <c r="A44">
         <v>9002</v>
       </c>
-      <c r="C44" t="s">
-        <v>80</v>
-      </c>
-      <c r="D44">
-        <v>1</v>
-      </c>
-      <c r="E44" t="s">
-        <v>309</v>
+      <c r="D44" t="s">
+        <v>31</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>310</v>
-      </c>
-      <c r="H44" t="s">
-        <v>311</v>
+        <v>246</v>
+      </c>
+      <c r="G44" t="s">
+        <v>247</v>
+      </c>
+      <c r="I44" t="s">
+        <v>248</v>
       </c>
       <c r="L44" t="s">
-        <v>312</v>
+        <v>249</v>
       </c>
       <c r="M44" t="s">
-        <v>313</v>
+        <v>250</v>
       </c>
     </row>
     <row r="45" spans="1:13">
       <c r="A45">
         <v>9003</v>
       </c>
-      <c r="C45" t="s">
-        <v>80</v>
-      </c>
-      <c r="D45">
-        <v>1</v>
-      </c>
-      <c r="E45" t="s">
-        <v>314</v>
+      <c r="D45" t="s">
+        <v>31</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>315</v>
-      </c>
-      <c r="H45" t="s">
-        <v>316</v>
+        <v>251</v>
+      </c>
+      <c r="G45" t="s">
+        <v>252</v>
+      </c>
+      <c r="I45" t="s">
+        <v>253</v>
       </c>
       <c r="L45" t="s">
-        <v>317</v>
+        <v>254</v>
       </c>
       <c r="M45" t="s">
-        <v>318</v>
+        <v>255</v>
       </c>
     </row>
     <row r="46" spans="1:13">
       <c r="A46">
         <v>9004</v>
       </c>
-      <c r="C46" t="s">
-        <v>80</v>
-      </c>
-      <c r="D46">
-        <v>1</v>
-      </c>
-      <c r="E46" t="s">
-        <v>319</v>
+      <c r="D46" t="s">
+        <v>31</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>320</v>
+        <v>256</v>
       </c>
       <c r="G46" t="s">
-        <v>321</v>
+        <v>257</v>
       </c>
       <c r="H46" t="s">
-        <v>322</v>
+        <v>258</v>
+      </c>
+      <c r="I46" t="s">
+        <v>259</v>
       </c>
       <c r="L46" t="s">
-        <v>323</v>
+        <v>260</v>
       </c>
       <c r="M46" t="s">
-        <v>324</v>
+        <v>261</v>
       </c>
     </row>
     <row r="47" spans="1:13">
       <c r="A47">
         <v>9005</v>
       </c>
-      <c r="C47" t="s">
-        <v>80</v>
-      </c>
-      <c r="D47">
-        <v>1</v>
-      </c>
-      <c r="E47" t="s">
-        <v>325</v>
+      <c r="D47" t="s">
+        <v>31</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>326</v>
-      </c>
-      <c r="H47" t="s">
-        <v>327</v>
+        <v>262</v>
+      </c>
+      <c r="G47" t="s">
+        <v>263</v>
+      </c>
+      <c r="I47" t="s">
+        <v>264</v>
       </c>
       <c r="L47" t="s">
-        <v>328</v>
+        <v>265</v>
       </c>
       <c r="M47" t="s">
-        <v>329</v>
+        <v>266</v>
       </c>
     </row>
     <row r="48" spans="1:13">
       <c r="A48">
         <v>9006</v>
       </c>
-      <c r="C48" t="s">
-        <v>80</v>
-      </c>
-      <c r="D48">
-        <v>1</v>
-      </c>
-      <c r="E48" t="s">
-        <v>330</v>
+      <c r="D48" t="s">
+        <v>31</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>331</v>
-      </c>
-      <c r="H48" t="s">
-        <v>332</v>
+        <v>267</v>
+      </c>
+      <c r="G48" t="s">
+        <v>268</v>
+      </c>
+      <c r="I48" t="s">
+        <v>269</v>
       </c>
       <c r="L48" t="s">
-        <v>333</v>
+        <v>270</v>
       </c>
       <c r="M48" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="49" spans="1:13">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="49" spans="1:15">
       <c r="A49">
         <v>9007</v>
       </c>
-      <c r="C49" t="s">
-        <v>80</v>
-      </c>
-      <c r="D49">
-        <v>1</v>
-      </c>
-      <c r="E49" t="s">
-        <v>335</v>
+      <c r="D49" t="s">
+        <v>31</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>336</v>
-      </c>
-      <c r="H49" t="s">
-        <v>337</v>
+        <v>272</v>
+      </c>
+      <c r="G49" t="s">
+        <v>273</v>
+      </c>
+      <c r="I49" t="s">
+        <v>274</v>
       </c>
       <c r="L49" t="s">
-        <v>338</v>
+        <v>275</v>
       </c>
       <c r="M49" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="50" spans="1:15">
       <c r="A50">
         <v>9008</v>
       </c>
-      <c r="C50" t="s">
-        <v>80</v>
-      </c>
-      <c r="D50">
-        <v>1</v>
-      </c>
-      <c r="E50" t="s">
-        <v>340</v>
+      <c r="D50" t="s">
+        <v>31</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>341</v>
-      </c>
-      <c r="H50" t="s">
-        <v>342</v>
+        <v>277</v>
+      </c>
+      <c r="G50" t="s">
+        <v>278</v>
+      </c>
+      <c r="I50" t="s">
+        <v>279</v>
       </c>
       <c r="L50" t="s">
-        <v>343</v>
+        <v>280</v>
       </c>
       <c r="M50" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="51" spans="1:15">
       <c r="A51">
         <v>9009</v>
       </c>
-      <c r="C51" t="s">
-        <v>80</v>
-      </c>
-      <c r="D51">
-        <v>1</v>
-      </c>
-      <c r="E51" t="s">
-        <v>345</v>
+      <c r="D51" t="s">
+        <v>31</v>
+      </c>
+      <c r="E51">
+        <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>346</v>
-      </c>
-      <c r="H51" t="s">
-        <v>347</v>
+        <v>282</v>
+      </c>
+      <c r="G51" t="s">
+        <v>283</v>
+      </c>
+      <c r="I51" t="s">
+        <v>284</v>
       </c>
       <c r="L51" t="s">
-        <v>348</v>
+        <v>285</v>
       </c>
       <c r="M51" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="52" spans="1:15">
       <c r="A52">
         <v>9010</v>
       </c>
-      <c r="C52" t="s">
-        <v>80</v>
-      </c>
-      <c r="D52">
-        <v>1</v>
-      </c>
-      <c r="E52" t="s">
-        <v>350</v>
+      <c r="D52" t="s">
+        <v>31</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
       </c>
       <c r="F52" t="s">
-        <v>351</v>
-      </c>
-      <c r="H52" t="s">
-        <v>352</v>
+        <v>287</v>
+      </c>
+      <c r="G52" t="s">
+        <v>288</v>
+      </c>
+      <c r="I52" t="s">
+        <v>289</v>
       </c>
       <c r="L52" t="s">
-        <v>353</v>
+        <v>290</v>
       </c>
       <c r="M52" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="53" spans="1:15">
       <c r="A53">
         <v>9011</v>
       </c>
-      <c r="C53" t="s">
-        <v>80</v>
-      </c>
-      <c r="D53">
-        <v>1</v>
-      </c>
-      <c r="E53" t="s">
-        <v>355</v>
+      <c r="D53" t="s">
+        <v>31</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>356</v>
-      </c>
-      <c r="H53" t="s">
-        <v>357</v>
+        <v>292</v>
+      </c>
+      <c r="G53" t="s">
+        <v>293</v>
+      </c>
+      <c r="I53" t="s">
+        <v>294</v>
       </c>
       <c r="L53" t="s">
-        <v>358</v>
+        <v>295</v>
       </c>
       <c r="M53" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="54" spans="1:15">
       <c r="A54">
         <v>9012</v>
       </c>
-      <c r="C54" t="s">
-        <v>80</v>
-      </c>
-      <c r="D54">
-        <v>1</v>
-      </c>
-      <c r="E54" t="s">
-        <v>360</v>
+      <c r="D54" t="s">
+        <v>31</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>361</v>
-      </c>
-      <c r="H54" t="s">
-        <v>362</v>
+        <v>297</v>
+      </c>
+      <c r="G54" t="s">
+        <v>298</v>
+      </c>
+      <c r="I54" t="s">
+        <v>299</v>
       </c>
       <c r="L54" t="s">
-        <v>363</v>
+        <v>300</v>
       </c>
       <c r="M54" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="55" spans="1:15">
       <c r="A55">
         <v>9013</v>
       </c>
-      <c r="C55" t="s">
-        <v>80</v>
-      </c>
-      <c r="D55">
-        <v>1</v>
-      </c>
-      <c r="E55" t="s">
-        <v>365</v>
+      <c r="D55" t="s">
+        <v>31</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
       </c>
       <c r="F55" t="s">
-        <v>366</v>
-      </c>
-      <c r="H55" t="s">
-        <v>367</v>
+        <v>302</v>
+      </c>
+      <c r="G55" t="s">
+        <v>303</v>
+      </c>
+      <c r="I55" t="s">
+        <v>304</v>
       </c>
       <c r="L55" t="s">
-        <v>368</v>
+        <v>305</v>
       </c>
       <c r="M55" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="56" spans="1:13">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="56" spans="1:15">
       <c r="A56">
         <v>9014</v>
       </c>
-      <c r="C56" t="s">
-        <v>80</v>
-      </c>
-      <c r="D56">
-        <v>1</v>
-      </c>
-      <c r="E56" t="s">
-        <v>370</v>
+      <c r="D56" t="s">
+        <v>31</v>
+      </c>
+      <c r="E56">
+        <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>371</v>
-      </c>
-      <c r="H56" t="s">
-        <v>372</v>
+        <v>307</v>
+      </c>
+      <c r="G56" t="s">
+        <v>308</v>
+      </c>
+      <c r="I56" t="s">
+        <v>309</v>
       </c>
       <c r="L56" t="s">
-        <v>373</v>
+        <v>310</v>
       </c>
       <c r="M56" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="57" spans="1:15">
       <c r="A57">
         <v>9015</v>
       </c>
-      <c r="C57" t="s">
-        <v>80</v>
-      </c>
-      <c r="D57">
-        <v>1</v>
-      </c>
-      <c r="E57" t="s">
-        <v>375</v>
+      <c r="D57" t="s">
+        <v>31</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
       </c>
       <c r="F57" t="s">
-        <v>376</v>
+        <v>312</v>
       </c>
       <c r="G57" t="s">
-        <v>377</v>
+        <v>313</v>
       </c>
       <c r="H57" t="s">
-        <v>378</v>
+        <v>314</v>
+      </c>
+      <c r="I57" t="s">
+        <v>315</v>
       </c>
       <c r="L57" t="s">
-        <v>379</v>
+        <v>316</v>
       </c>
       <c r="M57" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="58" spans="1:15">
       <c r="A58">
         <v>9016</v>
       </c>
-      <c r="C58" t="s">
-        <v>80</v>
-      </c>
-      <c r="D58">
-        <v>1</v>
-      </c>
-      <c r="E58" t="s">
-        <v>381</v>
+      <c r="D58" t="s">
+        <v>31</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
       </c>
       <c r="F58" t="s">
-        <v>382</v>
-      </c>
-      <c r="H58" t="s">
-        <v>383</v>
+        <v>318</v>
+      </c>
+      <c r="G58" t="s">
+        <v>319</v>
+      </c>
+      <c r="I58" t="s">
+        <v>320</v>
       </c>
       <c r="L58" t="s">
-        <v>384</v>
+        <v>321</v>
       </c>
       <c r="M58" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13">
+        <v>322</v>
+      </c>
+      <c r="O58" s="1"/>
+    </row>
+    <row r="59" spans="1:15">
       <c r="A59">
         <v>9017</v>
       </c>
-      <c r="C59" t="s">
-        <v>80</v>
-      </c>
-      <c r="D59">
-        <v>1</v>
-      </c>
-      <c r="E59" t="s">
-        <v>386</v>
+      <c r="D59" t="s">
+        <v>31</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
       </c>
       <c r="F59" t="s">
-        <v>387</v>
-      </c>
-      <c r="H59" t="s">
-        <v>388</v>
+        <v>323</v>
+      </c>
+      <c r="G59" t="s">
+        <v>324</v>
+      </c>
+      <c r="I59" t="s">
+        <v>325</v>
       </c>
       <c r="L59" t="s">
-        <v>389</v>
+        <v>326</v>
       </c>
       <c r="M59" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="60" spans="1:15">
       <c r="A60">
         <v>9018</v>
       </c>
-      <c r="C60" t="s">
-        <v>80</v>
-      </c>
-      <c r="D60">
-        <v>1</v>
-      </c>
-      <c r="E60" t="s">
-        <v>391</v>
+      <c r="D60" t="s">
+        <v>31</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
       </c>
       <c r="F60" t="s">
-        <v>392</v>
-      </c>
-      <c r="H60" t="s">
-        <v>393</v>
+        <v>328</v>
+      </c>
+      <c r="G60" t="s">
+        <v>329</v>
+      </c>
+      <c r="I60" t="s">
+        <v>330</v>
       </c>
       <c r="L60" t="s">
-        <v>394</v>
+        <v>331</v>
       </c>
       <c r="M60" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="61" spans="1:15">
       <c r="A61">
         <v>9019</v>
       </c>
-      <c r="C61" t="s">
-        <v>80</v>
-      </c>
-      <c r="D61">
-        <v>1</v>
-      </c>
-      <c r="E61" t="s">
-        <v>396</v>
+      <c r="D61" t="s">
+        <v>31</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
       </c>
       <c r="F61" t="s">
-        <v>397</v>
-      </c>
-      <c r="H61" t="s">
-        <v>398</v>
+        <v>333</v>
+      </c>
+      <c r="G61" t="s">
+        <v>334</v>
+      </c>
+      <c r="I61" t="s">
+        <v>335</v>
       </c>
       <c r="L61" t="s">
-        <v>399</v>
+        <v>336</v>
       </c>
       <c r="M61" t="s">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="62" spans="1:15">
       <c r="A62">
         <v>9020</v>
       </c>
-      <c r="C62" t="s">
-        <v>80</v>
-      </c>
-      <c r="D62">
-        <v>1</v>
-      </c>
-      <c r="E62" t="s">
-        <v>401</v>
+      <c r="D62" t="s">
+        <v>31</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
       </c>
       <c r="F62" t="s">
-        <v>402</v>
-      </c>
-      <c r="H62" t="s">
-        <v>403</v>
+        <v>338</v>
+      </c>
+      <c r="G62" t="s">
+        <v>339</v>
+      </c>
+      <c r="I62" t="s">
+        <v>340</v>
       </c>
       <c r="L62" t="s">
-        <v>404</v>
+        <v>341</v>
       </c>
       <c r="M62" t="s">
-        <v>405</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15">
       <c r="A63">
         <v>9021</v>
       </c>
-      <c r="C63" t="s">
-        <v>80</v>
-      </c>
-      <c r="D63">
-        <v>1</v>
-      </c>
-      <c r="E63" t="s">
-        <v>406</v>
+      <c r="D63" t="s">
+        <v>31</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
       </c>
       <c r="F63" t="s">
-        <v>407</v>
-      </c>
-      <c r="H63" t="s">
-        <v>408</v>
+        <v>343</v>
+      </c>
+      <c r="G63" t="s">
+        <v>344</v>
+      </c>
+      <c r="I63" t="s">
+        <v>345</v>
       </c>
       <c r="L63" t="s">
-        <v>409</v>
+        <v>346</v>
       </c>
       <c r="M63" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15">
       <c r="A64">
         <v>9022</v>
       </c>
-      <c r="C64" t="s">
-        <v>80</v>
-      </c>
-      <c r="D64">
-        <v>1</v>
-      </c>
-      <c r="E64" t="s">
-        <v>411</v>
+      <c r="D64" t="s">
+        <v>31</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
       </c>
       <c r="F64" t="s">
-        <v>412</v>
-      </c>
-      <c r="H64" t="s">
-        <v>413</v>
+        <v>348</v>
+      </c>
+      <c r="G64" t="s">
+        <v>349</v>
+      </c>
+      <c r="I64" t="s">
+        <v>350</v>
       </c>
       <c r="L64" t="s">
-        <v>414</v>
+        <v>351</v>
       </c>
       <c r="M64" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="65" spans="1:72">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17">
       <c r="A65">
         <v>9023</v>
       </c>
-      <c r="C65" t="s">
-        <v>416</v>
-      </c>
-      <c r="D65">
-        <v>1</v>
-      </c>
-      <c r="E65" t="s">
-        <v>417</v>
+      <c r="D65" t="s">
+        <v>353</v>
+      </c>
+      <c r="E65">
+        <v>1</v>
       </c>
       <c r="F65" t="s">
-        <v>418</v>
+        <v>354</v>
       </c>
       <c r="G65" t="s">
-        <v>419</v>
+        <v>355</v>
+      </c>
+      <c r="H65" t="s">
+        <v>356</v>
       </c>
       <c r="L65" t="s">
-        <v>420</v>
+        <v>357</v>
       </c>
       <c r="M65" t="s">
-        <v>421</v>
-      </c>
-      <c r="R65" t="s">
-        <v>422</v>
-      </c>
-      <c r="S65" t="s">
-        <v>423</v>
-      </c>
-      <c r="BS65" t="s">
-        <v>422</v>
-      </c>
-      <c r="BT65" t="s">
-        <v>423</v>
-      </c>
-    </row>
-    <row r="66" spans="1:72">
+        <v>358</v>
+      </c>
+      <c r="P65" t="s">
+        <v>359</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="66" spans="1:17">
       <c r="A66">
         <v>9024</v>
       </c>
-      <c r="C66" t="s">
-        <v>416</v>
-      </c>
-      <c r="D66">
-        <v>1</v>
-      </c>
-      <c r="E66" t="s">
-        <v>424</v>
+      <c r="D66" t="s">
+        <v>353</v>
+      </c>
+      <c r="E66">
+        <v>1</v>
       </c>
       <c r="F66" t="s">
-        <v>425</v>
+        <v>361</v>
       </c>
       <c r="G66" t="s">
-        <v>426</v>
+        <v>362</v>
+      </c>
+      <c r="H66" t="s">
+        <v>363</v>
       </c>
       <c r="L66" t="s">
-        <v>420</v>
+        <v>357</v>
       </c>
       <c r="M66" t="s">
-        <v>427</v>
-      </c>
-      <c r="R66" t="s">
-        <v>428</v>
-      </c>
-      <c r="S66" t="s">
-        <v>429</v>
-      </c>
-      <c r="BS66" t="s">
-        <v>428</v>
-      </c>
-      <c r="BT66" t="s">
-        <v>429</v>
+        <v>364</v>
+      </c>
+      <c r="P66" t="s">
+        <v>365</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>366</v>
       </c>
     </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:AE66" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <hyperlinks>
-    <hyperlink ref="G42" r:id="rId3" display="https://www.gzzx.gov.cn/images/iconcf134.ico"/>
-    <hyperlink ref="G46" r:id="rId4" display="http://www.jpzx.gov.cn/favicon.ico"/>
-    <hyperlink ref="G57" r:id="rId5" display="https://www.google.com/s2/favicons?domain=http://www.gdzjzx.gov.cn/"/>
-    <hyperlink ref="BT3" r:id="rId6" display="http://www.cppcc.gov.cn/"/>
-    <hyperlink ref="BT4" r:id="rId6" display="http://www.cppcc.gov.cn/"/>
-    <hyperlink ref="BT5" r:id="rId6" display="http://www.cppcc.gov.cn/"/>
-    <hyperlink ref="BT6" r:id="rId6" display="http://www.cppcc.gov.cn/"/>
-    <hyperlink ref="BT7" r:id="rId6" display="http://www.cppcc.gov.cn/"/>
-    <hyperlink ref="BT8" r:id="rId6" display="http://www.cppcc.gov.cn/"/>
-    <hyperlink ref="BT9" r:id="rId6" display="http://www.cppcc.gov.cn/"/>
-    <hyperlink ref="BT10" r:id="rId6" display="http://www.cppcc.gov.cn/"/>
-    <hyperlink ref="BV6" r:id="rId7" display="https://baike.baidu.com/item/%E4%B8%AD%E5%9B%BD%E6%B0%91%E4%B8%BB%E4%BF%83%E8%BF%9B%E4%BC%9A"/>
-    <hyperlink ref="BV7" r:id="rId8" display="https://baike.baidu.com/item/%E4%B8%AD%E5%9B%BD%E5%86%9C%E5%B7%A5%E6%B0%91%E4%B8%BB%E5%85%9A"/>
-    <hyperlink ref="BV8" r:id="rId9" display="https://baike.baidu.com/item/%E4%B8%AD%E5%9B%BD%E8%87%B4%E5%85%AC%E5%85%9A"/>
-    <hyperlink ref="BV9" r:id="rId10" display="https://baike.baidu.com/item/%E4%B9%9D%E4%B8%89%E5%AD%A6%E7%A4%BE"/>
-    <hyperlink ref="BV10" r:id="rId11" display="https://baike.baidu.com/item/%E5%8F%B0%E6%B9%BE%E6%B0%91%E4%B8%BB%E8%87%AA%E6%B2%BB%E5%90%8C%E7%9B%9F"/>
+    <hyperlink ref="G42" r:id="rId3" display="中国人民政治协商会议广州市委员会官方网站。提供政协动态、会议提案、委员履职等信息。本站为第三方导航，与官方无隶属关系，不对跳转后内容负责。"/>
+    <hyperlink ref="G46" r:id="rId4" display="中国人民政治协商会议汕头市金平区委员会官方网站。提供政协动态、会议提案、委员履职等信息。本站为第三方导航，与官方无隶属关系，不对跳转后内容负责。"/>
+    <hyperlink ref="G57" r:id="rId5" display="中国人民政治协商会议湛江市委员会官方网站。提供政协动态、会议提案、委员履职等信息。本站为第三方导航，与官方无隶属关系，不对跳转后内容负责。"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
